--- a/criterion_property_definitions.xlsx
+++ b/criterion_property_definitions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\configuration\master-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E86A9643-53EC-449C-950C-21472ECD83CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BEF0077-2C24-42D9-BD93-6940AED9DFEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="31395" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="48570" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="criterion_property" sheetId="4" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1833" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="459">
   <si>
     <t>property</t>
   </si>
@@ -1402,6 +1402,9 @@
   </si>
   <si>
     <t>proband.trialParticipations.ecrfValues.modifiedUser.id</t>
+  </si>
+  <si>
+    <t>staff.personParticulars.cvAcademicTitle</t>
   </si>
 </sst>
 </file>
@@ -1778,7 +1781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M305"/>
+  <dimension ref="A1:M306"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="15.7109375" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
@@ -2365,13 +2368,13 @@
         <v>20</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>458</v>
       </c>
       <c r="C28" t="s">
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>31</v>
+        <v>458</v>
       </c>
       <c r="M28" t="s">
         <v>122</v>
@@ -2382,16 +2385,16 @@
         <v>20</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M29" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2399,16 +2402,16 @@
         <v>20</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C30" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="L30" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="M30" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2416,13 +2419,13 @@
         <v>20</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C31" t="s">
         <v>17</v>
       </c>
       <c r="L31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M31" t="s">
         <v>121</v>
@@ -2433,13 +2436,13 @@
         <v>20</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C32" t="s">
         <v>17</v>
       </c>
       <c r="L32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M32" t="s">
         <v>121</v>
@@ -2450,13 +2453,13 @@
         <v>20</v>
       </c>
       <c r="B33" t="s">
-        <v>263</v>
+        <v>36</v>
       </c>
       <c r="C33" t="s">
         <v>17</v>
       </c>
       <c r="L33" t="s">
-        <v>263</v>
+        <v>36</v>
       </c>
       <c r="M33" t="s">
         <v>121</v>
@@ -2467,19 +2470,16 @@
         <v>20</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>9</v>
-      </c>
-      <c r="K34" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L34" t="s">
-        <v>37</v>
+        <v>263</v>
       </c>
       <c r="M34" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2487,19 +2487,19 @@
         <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35" t="s">
         <v>9</v>
       </c>
       <c r="K35" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="L35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M35" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2507,16 +2507,16 @@
         <v>20</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C36" t="s">
         <v>9</v>
       </c>
       <c r="K36" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L36" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M36" t="s">
         <v>121</v>
@@ -2527,19 +2527,16 @@
         <v>20</v>
       </c>
       <c r="B37" t="s">
-        <v>211</v>
+        <v>40</v>
       </c>
       <c r="C37" t="s">
         <v>9</v>
       </c>
-      <c r="D37" t="s">
-        <v>311</v>
-      </c>
-      <c r="J37" t="s">
-        <v>417</v>
+      <c r="K37" t="s">
+        <v>41</v>
       </c>
       <c r="L37" t="s">
-        <v>211</v>
+        <v>40</v>
       </c>
       <c r="M37" t="s">
         <v>121</v>
@@ -2550,16 +2547,19 @@
         <v>20</v>
       </c>
       <c r="B38" t="s">
-        <v>255</v>
+        <v>211</v>
       </c>
       <c r="C38" t="s">
         <v>9</v>
       </c>
-      <c r="K38" t="s">
-        <v>39</v>
+      <c r="D38" t="s">
+        <v>311</v>
+      </c>
+      <c r="J38" t="s">
+        <v>417</v>
       </c>
       <c r="L38" t="s">
-        <v>255</v>
+        <v>211</v>
       </c>
       <c r="M38" t="s">
         <v>121</v>
@@ -2570,16 +2570,19 @@
         <v>20</v>
       </c>
       <c r="B39" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C39" t="s">
-        <v>33</v>
+        <v>9</v>
+      </c>
+      <c r="K39" t="s">
+        <v>39</v>
       </c>
       <c r="L39" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="M39" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2590,19 +2593,13 @@
         <v>250</v>
       </c>
       <c r="C40" t="s">
-        <v>15</v>
-      </c>
-      <c r="D40" t="s">
-        <v>308</v>
-      </c>
-      <c r="J40" t="s">
-        <v>438</v>
+        <v>33</v>
       </c>
       <c r="L40" t="s">
-        <v>251</v>
-      </c>
-      <c r="M40" s="1" t="s">
-        <v>244</v>
+        <v>250</v>
+      </c>
+      <c r="M40" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2610,16 +2607,22 @@
         <v>20</v>
       </c>
       <c r="B41" t="s">
-        <v>144</v>
+        <v>250</v>
       </c>
       <c r="C41" t="s">
-        <v>9</v>
+        <v>15</v>
+      </c>
+      <c r="D41" t="s">
+        <v>308</v>
+      </c>
+      <c r="J41" t="s">
+        <v>438</v>
       </c>
       <c r="L41" t="s">
-        <v>144</v>
-      </c>
-      <c r="M41" t="s">
-        <v>125</v>
+        <v>251</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2627,13 +2630,13 @@
         <v>20</v>
       </c>
       <c r="B42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C42" t="s">
         <v>9</v>
       </c>
       <c r="L42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M42" t="s">
         <v>125</v>
@@ -2644,22 +2647,16 @@
         <v>20</v>
       </c>
       <c r="B43" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C43" t="s">
         <v>9</v>
       </c>
-      <c r="D43" t="s">
-        <v>312</v>
-      </c>
-      <c r="J43" t="s">
-        <v>418</v>
-      </c>
       <c r="L43" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="M43" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2667,16 +2664,22 @@
         <v>20</v>
       </c>
       <c r="B44" t="s">
-        <v>42</v>
+        <v>146</v>
       </c>
       <c r="C44" t="s">
-        <v>15</v>
+        <v>9</v>
+      </c>
+      <c r="D44" t="s">
+        <v>312</v>
+      </c>
+      <c r="J44" t="s">
+        <v>418</v>
       </c>
       <c r="L44" t="s">
-        <v>42</v>
+        <v>146</v>
       </c>
       <c r="M44" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2684,28 +2687,16 @@
         <v>20</v>
       </c>
       <c r="B45" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C45" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" t="s">
-        <v>313</v>
-      </c>
-      <c r="E45" t="s">
-        <v>44</v>
-      </c>
-      <c r="F45" t="s">
-        <v>11</v>
-      </c>
-      <c r="G45" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M45" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2713,16 +2704,28 @@
         <v>20</v>
       </c>
       <c r="B46" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C46" t="s">
         <v>9</v>
       </c>
+      <c r="D46" t="s">
+        <v>313</v>
+      </c>
+      <c r="E46" t="s">
+        <v>44</v>
+      </c>
+      <c r="F46" t="s">
+        <v>11</v>
+      </c>
+      <c r="G46" t="s">
+        <v>12</v>
+      </c>
       <c r="L46" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M46" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2730,16 +2733,16 @@
         <v>20</v>
       </c>
       <c r="B47" t="s">
-        <v>157</v>
+        <v>45</v>
       </c>
       <c r="C47" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="L47" t="s">
-        <v>157</v>
+        <v>45</v>
       </c>
       <c r="M47" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2747,22 +2750,16 @@
         <v>20</v>
       </c>
       <c r="B48" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C48" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" t="s">
-        <v>314</v>
-      </c>
-      <c r="J48" t="s">
-        <v>430</v>
+        <v>15</v>
       </c>
       <c r="L48" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="M48" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2770,16 +2767,22 @@
         <v>20</v>
       </c>
       <c r="B49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C49" t="s">
         <v>9</v>
       </c>
+      <c r="D49" t="s">
+        <v>314</v>
+      </c>
+      <c r="J49" t="s">
+        <v>430</v>
+      </c>
       <c r="L49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M49" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2787,16 +2790,16 @@
         <v>20</v>
       </c>
       <c r="B50" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C50" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="L50" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M50" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2804,16 +2807,16 @@
         <v>20</v>
       </c>
       <c r="B51" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="C51" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L51" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="M51" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2821,16 +2824,16 @@
         <v>20</v>
       </c>
       <c r="B52" t="s">
-        <v>212</v>
+        <v>147</v>
       </c>
       <c r="C52" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="L52" t="s">
-        <v>212</v>
+        <v>147</v>
       </c>
       <c r="M52" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2841,19 +2844,13 @@
         <v>212</v>
       </c>
       <c r="C53" t="s">
-        <v>15</v>
-      </c>
-      <c r="D53" t="s">
-        <v>308</v>
-      </c>
-      <c r="J53" t="s">
-        <v>438</v>
+        <v>52</v>
       </c>
       <c r="L53" t="s">
-        <v>242</v>
-      </c>
-      <c r="M53" s="1" t="s">
-        <v>245</v>
+        <v>212</v>
+      </c>
+      <c r="M53" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2861,16 +2858,22 @@
         <v>20</v>
       </c>
       <c r="B54" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C54" t="s">
-        <v>52</v>
+        <v>15</v>
+      </c>
+      <c r="D54" t="s">
+        <v>308</v>
+      </c>
+      <c r="J54" t="s">
+        <v>438</v>
       </c>
       <c r="L54" t="s">
-        <v>213</v>
-      </c>
-      <c r="M54" t="s">
-        <v>246</v>
+        <v>242</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2881,19 +2884,13 @@
         <v>213</v>
       </c>
       <c r="C55" t="s">
-        <v>15</v>
-      </c>
-      <c r="D55" t="s">
-        <v>308</v>
-      </c>
-      <c r="J55" t="s">
-        <v>438</v>
+        <v>52</v>
       </c>
       <c r="L55" t="s">
-        <v>241</v>
-      </c>
-      <c r="M55" s="1" t="s">
-        <v>245</v>
+        <v>213</v>
+      </c>
+      <c r="M55" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2901,22 +2898,22 @@
         <v>20</v>
       </c>
       <c r="B56" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C56" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D56" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="J56" t="s">
-        <v>419</v>
+        <v>438</v>
       </c>
       <c r="L56" t="s">
-        <v>214</v>
-      </c>
-      <c r="M56" t="s">
-        <v>121</v>
+        <v>241</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2924,13 +2921,19 @@
         <v>20</v>
       </c>
       <c r="B57" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C57" t="s">
-        <v>17</v>
+        <v>9</v>
+      </c>
+      <c r="D57" t="s">
+        <v>315</v>
+      </c>
+      <c r="J57" t="s">
+        <v>419</v>
       </c>
       <c r="L57" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M57" t="s">
         <v>121</v>
@@ -2941,16 +2944,13 @@
         <v>20</v>
       </c>
       <c r="B58" t="s">
-        <v>252</v>
+        <v>215</v>
       </c>
       <c r="C58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K58" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="L58" t="s">
-        <v>252</v>
+        <v>215</v>
       </c>
       <c r="M58" t="s">
         <v>121</v>
@@ -2961,16 +2961,19 @@
         <v>20</v>
       </c>
       <c r="B59" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C59" t="s">
-        <v>52</v>
+        <v>9</v>
+      </c>
+      <c r="K59" t="s">
+        <v>39</v>
       </c>
       <c r="L59" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="M59" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2981,19 +2984,13 @@
         <v>253</v>
       </c>
       <c r="C60" t="s">
-        <v>15</v>
-      </c>
-      <c r="D60" t="s">
-        <v>308</v>
-      </c>
-      <c r="J60" t="s">
-        <v>438</v>
+        <v>52</v>
       </c>
       <c r="L60" t="s">
-        <v>256</v>
-      </c>
-      <c r="M60" s="1" t="s">
-        <v>245</v>
+        <v>253</v>
+      </c>
+      <c r="M60" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3001,16 +2998,22 @@
         <v>20</v>
       </c>
       <c r="B61" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C61" t="s">
-        <v>52</v>
+        <v>15</v>
+      </c>
+      <c r="D61" t="s">
+        <v>308</v>
+      </c>
+      <c r="J61" t="s">
+        <v>438</v>
       </c>
       <c r="L61" t="s">
-        <v>254</v>
-      </c>
-      <c r="M61" t="s">
-        <v>127</v>
+        <v>256</v>
+      </c>
+      <c r="M61" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3021,36 +3024,36 @@
         <v>254</v>
       </c>
       <c r="C62" t="s">
-        <v>15</v>
-      </c>
-      <c r="D62" t="s">
-        <v>308</v>
-      </c>
-      <c r="J62" t="s">
-        <v>438</v>
+        <v>52</v>
       </c>
       <c r="L62" t="s">
-        <v>257</v>
-      </c>
-      <c r="M62" s="1" t="s">
-        <v>245</v>
+        <v>254</v>
+      </c>
+      <c r="M62" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="B63" t="s">
-        <v>46</v>
+        <v>254</v>
       </c>
       <c r="C63" t="s">
-        <v>9</v>
+        <v>15</v>
+      </c>
+      <c r="D63" t="s">
+        <v>308</v>
+      </c>
+      <c r="J63" t="s">
+        <v>438</v>
       </c>
       <c r="L63" t="s">
-        <v>46</v>
-      </c>
-      <c r="M63" t="s">
-        <v>120</v>
+        <v>257</v>
+      </c>
+      <c r="M63" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3058,28 +3061,16 @@
         <v>41</v>
       </c>
       <c r="B64" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C64" t="s">
         <v>9</v>
       </c>
-      <c r="D64" t="s">
-        <v>305</v>
-      </c>
-      <c r="F64" t="s">
-        <v>11</v>
-      </c>
-      <c r="H64" t="s">
-        <v>448</v>
-      </c>
-      <c r="I64" t="s">
-        <v>447</v>
-      </c>
       <c r="L64" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M64" t="s">
-        <v>149</v>
+        <v>120</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3087,22 +3078,28 @@
         <v>41</v>
       </c>
       <c r="B65" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C65" t="s">
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>311</v>
-      </c>
-      <c r="J65" t="s">
-        <v>417</v>
+        <v>305</v>
+      </c>
+      <c r="F65" t="s">
+        <v>11</v>
+      </c>
+      <c r="H65" t="s">
+        <v>448</v>
+      </c>
+      <c r="I65" t="s">
+        <v>447</v>
       </c>
       <c r="L65" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M65" t="s">
-        <v>121</v>
+        <v>149</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3110,16 +3107,19 @@
         <v>41</v>
       </c>
       <c r="B66" t="s">
-        <v>193</v>
+        <v>48</v>
       </c>
       <c r="C66" t="s">
         <v>9</v>
       </c>
-      <c r="K66" t="s">
-        <v>39</v>
+      <c r="D66" t="s">
+        <v>311</v>
+      </c>
+      <c r="J66" t="s">
+        <v>417</v>
       </c>
       <c r="L66" t="s">
-        <v>193</v>
+        <v>48</v>
       </c>
       <c r="M66" t="s">
         <v>121</v>
@@ -3130,16 +3130,19 @@
         <v>41</v>
       </c>
       <c r="B67" t="s">
-        <v>49</v>
+        <v>193</v>
       </c>
       <c r="C67" t="s">
-        <v>15</v>
+        <v>9</v>
+      </c>
+      <c r="K67" t="s">
+        <v>39</v>
       </c>
       <c r="L67" t="s">
-        <v>49</v>
+        <v>193</v>
       </c>
       <c r="M67" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3147,16 +3150,16 @@
         <v>41</v>
       </c>
       <c r="B68" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C68" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M68" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3167,19 +3170,13 @@
         <v>50</v>
       </c>
       <c r="C69" t="s">
-        <v>15</v>
-      </c>
-      <c r="D69" t="s">
-        <v>308</v>
-      </c>
-      <c r="J69" t="s">
-        <v>438</v>
+        <v>33</v>
       </c>
       <c r="L69" t="s">
-        <v>222</v>
-      </c>
-      <c r="M69" s="1" t="s">
-        <v>244</v>
+        <v>50</v>
+      </c>
+      <c r="M69" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3187,16 +3184,22 @@
         <v>41</v>
       </c>
       <c r="B70" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C70" t="s">
-        <v>52</v>
+        <v>15</v>
+      </c>
+      <c r="D70" t="s">
+        <v>308</v>
+      </c>
+      <c r="J70" t="s">
+        <v>438</v>
       </c>
       <c r="L70" t="s">
-        <v>51</v>
-      </c>
-      <c r="M70" t="s">
-        <v>127</v>
+        <v>222</v>
+      </c>
+      <c r="M70" s="1" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3207,19 +3210,13 @@
         <v>51</v>
       </c>
       <c r="C71" t="s">
-        <v>15</v>
-      </c>
-      <c r="D71" t="s">
-        <v>308</v>
-      </c>
-      <c r="J71" t="s">
-        <v>438</v>
+        <v>52</v>
       </c>
       <c r="L71" t="s">
-        <v>240</v>
-      </c>
-      <c r="M71" s="1" t="s">
-        <v>245</v>
+        <v>51</v>
+      </c>
+      <c r="M71" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3227,16 +3224,22 @@
         <v>41</v>
       </c>
       <c r="B72" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C72" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+      <c r="D72" t="s">
+        <v>308</v>
+      </c>
+      <c r="J72" t="s">
+        <v>438</v>
       </c>
       <c r="L72" t="s">
-        <v>53</v>
-      </c>
-      <c r="M72" t="s">
-        <v>121</v>
+        <v>240</v>
+      </c>
+      <c r="M72" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3244,13 +3247,13 @@
         <v>41</v>
       </c>
       <c r="B73" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C73" t="s">
         <v>17</v>
       </c>
       <c r="L73" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M73" t="s">
         <v>121</v>
@@ -3261,19 +3264,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C74" t="s">
-        <v>15</v>
-      </c>
-      <c r="D74" t="s">
-        <v>308</v>
-      </c>
-      <c r="J74" t="s">
-        <v>439</v>
+        <v>17</v>
       </c>
       <c r="L74" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M74" t="s">
         <v>121</v>
@@ -3284,13 +3281,19 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>143</v>
+        <v>55</v>
       </c>
       <c r="C75" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+      <c r="D75" t="s">
+        <v>308</v>
+      </c>
+      <c r="J75" t="s">
+        <v>439</v>
       </c>
       <c r="L75" t="s">
-        <v>143</v>
+        <v>55</v>
       </c>
       <c r="M75" t="s">
         <v>121</v>
@@ -3301,16 +3304,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>56</v>
+        <v>143</v>
       </c>
       <c r="C76" t="s">
-        <v>9</v>
-      </c>
-      <c r="K76" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="L76" t="s">
-        <v>56</v>
+        <v>143</v>
       </c>
       <c r="M76" t="s">
         <v>121</v>
@@ -3321,13 +3321,16 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>264</v>
+        <v>56</v>
       </c>
       <c r="C77" t="s">
-        <v>17</v>
+        <v>9</v>
+      </c>
+      <c r="K77" t="s">
+        <v>41</v>
       </c>
       <c r="L77" t="s">
-        <v>264</v>
+        <v>56</v>
       </c>
       <c r="M77" t="s">
         <v>121</v>
@@ -3338,16 +3341,16 @@
         <v>41</v>
       </c>
       <c r="B78" t="s">
-        <v>57</v>
+        <v>264</v>
       </c>
       <c r="C78" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L78" t="s">
-        <v>57</v>
+        <v>264</v>
       </c>
       <c r="M78" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="79" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3355,19 +3358,16 @@
         <v>41</v>
       </c>
       <c r="B79" t="s">
-        <v>137</v>
+        <v>57</v>
       </c>
       <c r="C79" t="s">
         <v>9</v>
       </c>
-      <c r="K79" t="s">
-        <v>41</v>
-      </c>
       <c r="L79" t="s">
-        <v>137</v>
+        <v>57</v>
       </c>
       <c r="M79" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3375,16 +3375,19 @@
         <v>41</v>
       </c>
       <c r="B80" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C80" t="s">
         <v>9</v>
       </c>
+      <c r="K80" t="s">
+        <v>41</v>
+      </c>
       <c r="L80" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M80" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="81" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3392,19 +3395,16 @@
         <v>41</v>
       </c>
       <c r="B81" t="s">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="C81" t="s">
         <v>9</v>
       </c>
-      <c r="K81" t="s">
-        <v>20</v>
-      </c>
       <c r="L81" t="s">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="M81" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="82" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3412,33 +3412,36 @@
         <v>41</v>
       </c>
       <c r="B82" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C82" t="s">
         <v>9</v>
       </c>
+      <c r="K82" t="s">
+        <v>20</v>
+      </c>
       <c r="L82" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M82" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B83" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C83" t="s">
         <v>9</v>
       </c>
       <c r="L83" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M83" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3446,28 +3449,16 @@
         <v>39</v>
       </c>
       <c r="B84" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C84" t="s">
         <v>9</v>
       </c>
-      <c r="D84" t="s">
-        <v>305</v>
-      </c>
-      <c r="F84" t="s">
-        <v>11</v>
-      </c>
-      <c r="H84" t="s">
-        <v>448</v>
-      </c>
-      <c r="I84" t="s">
-        <v>447</v>
-      </c>
       <c r="L84" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M84" t="s">
-        <v>149</v>
+        <v>120</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3475,16 +3466,28 @@
         <v>39</v>
       </c>
       <c r="B85" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C85" t="s">
-        <v>15</v>
+        <v>9</v>
+      </c>
+      <c r="D85" t="s">
+        <v>305</v>
+      </c>
+      <c r="F85" t="s">
+        <v>11</v>
+      </c>
+      <c r="H85" t="s">
+        <v>448</v>
+      </c>
+      <c r="I85" t="s">
+        <v>447</v>
       </c>
       <c r="L85" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M85" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3492,22 +3495,16 @@
         <v>39</v>
       </c>
       <c r="B86" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C86" t="s">
-        <v>9</v>
-      </c>
-      <c r="D86" t="s">
-        <v>316</v>
-      </c>
-      <c r="J86" t="s">
-        <v>420</v>
+        <v>15</v>
       </c>
       <c r="L86" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M86" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="87" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3515,19 +3512,19 @@
         <v>39</v>
       </c>
       <c r="B87" t="s">
-        <v>174</v>
+        <v>63</v>
       </c>
       <c r="C87" t="s">
         <v>9</v>
       </c>
       <c r="D87" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="J87" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L87" t="s">
-        <v>174</v>
+        <v>63</v>
       </c>
       <c r="M87" t="s">
         <v>121</v>
@@ -3538,19 +3535,19 @@
         <v>39</v>
       </c>
       <c r="B88" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C88" t="s">
         <v>9</v>
       </c>
       <c r="D88" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J88" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L88" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M88" t="s">
         <v>121</v>
@@ -3561,13 +3558,19 @@
         <v>39</v>
       </c>
       <c r="B89" t="s">
-        <v>209</v>
+        <v>175</v>
       </c>
       <c r="C89" t="s">
-        <v>17</v>
+        <v>9</v>
+      </c>
+      <c r="D89" t="s">
+        <v>318</v>
+      </c>
+      <c r="J89" t="s">
+        <v>422</v>
       </c>
       <c r="L89" t="s">
-        <v>209</v>
+        <v>175</v>
       </c>
       <c r="M89" t="s">
         <v>121</v>
@@ -3578,16 +3581,16 @@
         <v>39</v>
       </c>
       <c r="B90" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C90" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="L90" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M90" t="s">
-        <v>246</v>
+        <v>121</v>
       </c>
     </row>
     <row r="91" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3598,19 +3601,13 @@
         <v>210</v>
       </c>
       <c r="C91" t="s">
-        <v>15</v>
-      </c>
-      <c r="D91" t="s">
-        <v>308</v>
-      </c>
-      <c r="J91" t="s">
-        <v>438</v>
+        <v>52</v>
       </c>
       <c r="L91" t="s">
-        <v>239</v>
-      </c>
-      <c r="M91" s="1" t="s">
-        <v>245</v>
+        <v>210</v>
+      </c>
+      <c r="M91" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="92" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3618,16 +3615,22 @@
         <v>39</v>
       </c>
       <c r="B92" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="C92" t="s">
-        <v>52</v>
+        <v>15</v>
+      </c>
+      <c r="D92" t="s">
+        <v>308</v>
+      </c>
+      <c r="J92" t="s">
+        <v>438</v>
       </c>
       <c r="L92" t="s">
-        <v>223</v>
-      </c>
-      <c r="M92" t="s">
-        <v>246</v>
+        <v>239</v>
+      </c>
+      <c r="M92" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="93" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3638,19 +3641,13 @@
         <v>223</v>
       </c>
       <c r="C93" t="s">
-        <v>15</v>
-      </c>
-      <c r="D93" t="s">
-        <v>308</v>
-      </c>
-      <c r="J93" t="s">
-        <v>438</v>
+        <v>52</v>
       </c>
       <c r="L93" t="s">
-        <v>238</v>
-      </c>
-      <c r="M93" s="1" t="s">
-        <v>245</v>
+        <v>223</v>
+      </c>
+      <c r="M93" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3658,22 +3655,22 @@
         <v>39</v>
       </c>
       <c r="B94" t="s">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="C94" t="s">
         <v>15</v>
       </c>
       <c r="D94" t="s">
-        <v>409</v>
+        <v>308</v>
       </c>
       <c r="J94" t="s">
-        <v>423</v>
+        <v>438</v>
       </c>
       <c r="L94" t="s">
-        <v>408</v>
-      </c>
-      <c r="M94" t="s">
-        <v>121</v>
+        <v>238</v>
+      </c>
+      <c r="M94" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3681,13 +3678,19 @@
         <v>39</v>
       </c>
       <c r="B95" t="s">
-        <v>208</v>
+        <v>408</v>
       </c>
       <c r="C95" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+      <c r="D95" t="s">
+        <v>409</v>
+      </c>
+      <c r="J95" t="s">
+        <v>423</v>
       </c>
       <c r="L95" t="s">
-        <v>208</v>
+        <v>408</v>
       </c>
       <c r="M95" t="s">
         <v>121</v>
@@ -3698,13 +3701,13 @@
         <v>39</v>
       </c>
       <c r="B96" t="s">
-        <v>360</v>
+        <v>208</v>
       </c>
       <c r="C96" t="s">
         <v>17</v>
       </c>
       <c r="L96" t="s">
-        <v>360</v>
+        <v>208</v>
       </c>
       <c r="M96" t="s">
         <v>121</v>
@@ -3715,13 +3718,13 @@
         <v>39</v>
       </c>
       <c r="B97" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C97" t="s">
         <v>17</v>
       </c>
       <c r="L97" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="M97" t="s">
         <v>121</v>
@@ -3732,13 +3735,13 @@
         <v>39</v>
       </c>
       <c r="B98" t="s">
-        <v>265</v>
+        <v>361</v>
       </c>
       <c r="C98" t="s">
         <v>17</v>
       </c>
       <c r="L98" t="s">
-        <v>265</v>
+        <v>361</v>
       </c>
       <c r="M98" t="s">
         <v>121</v>
@@ -3749,19 +3752,13 @@
         <v>39</v>
       </c>
       <c r="B99" t="s">
-        <v>176</v>
+        <v>265</v>
       </c>
       <c r="C99" t="s">
-        <v>9</v>
-      </c>
-      <c r="D99" t="s">
-        <v>319</v>
-      </c>
-      <c r="J99" t="s">
-        <v>424</v>
+        <v>17</v>
       </c>
       <c r="L99" t="s">
-        <v>176</v>
+        <v>265</v>
       </c>
       <c r="M99" t="s">
         <v>121</v>
@@ -3772,19 +3769,22 @@
         <v>39</v>
       </c>
       <c r="B100" t="s">
-        <v>64</v>
+        <v>176</v>
       </c>
       <c r="C100" t="s">
         <v>9</v>
       </c>
-      <c r="K100" t="s">
-        <v>20</v>
+      <c r="D100" t="s">
+        <v>319</v>
+      </c>
+      <c r="J100" t="s">
+        <v>424</v>
       </c>
       <c r="L100" t="s">
-        <v>64</v>
+        <v>176</v>
       </c>
       <c r="M100" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="101" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3792,22 +3792,19 @@
         <v>39</v>
       </c>
       <c r="B101" t="s">
-        <v>183</v>
+        <v>64</v>
       </c>
       <c r="C101" t="s">
         <v>9</v>
       </c>
-      <c r="D101" t="s">
-        <v>320</v>
-      </c>
-      <c r="J101" t="s">
-        <v>425</v>
+      <c r="K101" t="s">
+        <v>20</v>
       </c>
       <c r="L101" t="s">
-        <v>183</v>
+        <v>64</v>
       </c>
       <c r="M101" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="102" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3815,16 +3812,22 @@
         <v>39</v>
       </c>
       <c r="B102" t="s">
-        <v>65</v>
+        <v>183</v>
       </c>
       <c r="C102" t="s">
         <v>9</v>
       </c>
+      <c r="D102" t="s">
+        <v>320</v>
+      </c>
+      <c r="J102" t="s">
+        <v>425</v>
+      </c>
       <c r="L102" t="s">
-        <v>65</v>
+        <v>183</v>
       </c>
       <c r="M102" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3832,19 +3835,16 @@
         <v>39</v>
       </c>
       <c r="B103" t="s">
-        <v>442</v>
+        <v>65</v>
       </c>
       <c r="C103" t="s">
         <v>9</v>
       </c>
-      <c r="J103" t="s">
-        <v>443</v>
-      </c>
       <c r="L103" t="s">
-        <v>444</v>
+        <v>65</v>
       </c>
       <c r="M103" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="104" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3852,16 +3852,19 @@
         <v>39</v>
       </c>
       <c r="B104" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C104" t="s">
-        <v>52</v>
+        <v>9</v>
+      </c>
+      <c r="J104" t="s">
+        <v>443</v>
       </c>
       <c r="L104" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="M104" t="s">
-        <v>246</v>
+        <v>121</v>
       </c>
     </row>
     <row r="105" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3872,19 +3875,13 @@
         <v>441</v>
       </c>
       <c r="C105" t="s">
-        <v>15</v>
-      </c>
-      <c r="D105" t="s">
-        <v>308</v>
-      </c>
-      <c r="J105" t="s">
-        <v>438</v>
+        <v>52</v>
       </c>
       <c r="L105" t="s">
-        <v>445</v>
-      </c>
-      <c r="M105" s="1" t="s">
-        <v>245</v>
+        <v>441</v>
+      </c>
+      <c r="M105" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="106" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3892,19 +3889,22 @@
         <v>39</v>
       </c>
       <c r="B106" t="s">
-        <v>258</v>
+        <v>441</v>
       </c>
       <c r="C106" t="s">
-        <v>9</v>
-      </c>
-      <c r="K106" t="s">
-        <v>77</v>
+        <v>15</v>
+      </c>
+      <c r="D106" t="s">
+        <v>308</v>
+      </c>
+      <c r="J106" t="s">
+        <v>438</v>
       </c>
       <c r="L106" t="s">
-        <v>258</v>
-      </c>
-      <c r="M106" t="s">
-        <v>121</v>
+        <v>445</v>
+      </c>
+      <c r="M106" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3912,16 +3912,19 @@
         <v>39</v>
       </c>
       <c r="B107" t="s">
-        <v>66</v>
+        <v>258</v>
       </c>
       <c r="C107" t="s">
         <v>9</v>
       </c>
+      <c r="K107" t="s">
+        <v>77</v>
+      </c>
       <c r="L107" t="s">
-        <v>66</v>
+        <v>258</v>
       </c>
       <c r="M107" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="108" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3929,16 +3932,16 @@
         <v>39</v>
       </c>
       <c r="B108" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C108" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="L108" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M108" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="109" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3946,28 +3949,16 @@
         <v>39</v>
       </c>
       <c r="B109" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C109" t="s">
-        <v>9</v>
-      </c>
-      <c r="D109" t="s">
-        <v>321</v>
-      </c>
-      <c r="E109" t="s">
-        <v>69</v>
-      </c>
-      <c r="F109" t="s">
-        <v>11</v>
-      </c>
-      <c r="G109" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L109" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M109" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="110" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3975,16 +3966,28 @@
         <v>39</v>
       </c>
       <c r="B110" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C110" t="s">
         <v>9</v>
       </c>
+      <c r="D110" t="s">
+        <v>321</v>
+      </c>
+      <c r="E110" t="s">
+        <v>69</v>
+      </c>
+      <c r="F110" t="s">
+        <v>11</v>
+      </c>
+      <c r="G110" t="s">
+        <v>12</v>
+      </c>
       <c r="L110" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="M110" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="111" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3992,13 +3995,13 @@
         <v>39</v>
       </c>
       <c r="B111" t="s">
-        <v>259</v>
+        <v>70</v>
       </c>
       <c r="C111" t="s">
         <v>9</v>
       </c>
       <c r="L111" t="s">
-        <v>259</v>
+        <v>70</v>
       </c>
       <c r="M111" t="s">
         <v>125</v>
@@ -4009,13 +4012,13 @@
         <v>39</v>
       </c>
       <c r="B112" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C112" t="s">
         <v>9</v>
       </c>
       <c r="L112" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M112" t="s">
         <v>125</v>
@@ -4023,19 +4026,19 @@
     </row>
     <row r="113" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="B113" t="s">
-        <v>72</v>
+        <v>260</v>
       </c>
       <c r="C113" t="s">
         <v>9</v>
       </c>
       <c r="L113" t="s">
-        <v>72</v>
+        <v>260</v>
       </c>
       <c r="M113" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="114" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4043,16 +4046,16 @@
         <v>71</v>
       </c>
       <c r="B114" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C114" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="L114" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M114" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="115" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4060,13 +4063,13 @@
         <v>71</v>
       </c>
       <c r="B115" t="s">
-        <v>377</v>
+        <v>73</v>
       </c>
       <c r="C115" t="s">
         <v>15</v>
       </c>
       <c r="L115" t="s">
-        <v>377</v>
+        <v>73</v>
       </c>
       <c r="M115" t="s">
         <v>122</v>
@@ -4077,13 +4080,13 @@
         <v>71</v>
       </c>
       <c r="B116" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C116" t="s">
         <v>15</v>
       </c>
       <c r="L116" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="M116" t="s">
         <v>122</v>
@@ -4094,33 +4097,33 @@
         <v>71</v>
       </c>
       <c r="B117" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C117" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L117" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="M117" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="118" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>292</v>
+        <v>71</v>
       </c>
       <c r="B118" t="s">
-        <v>281</v>
+        <v>379</v>
       </c>
       <c r="C118" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L118" t="s">
-        <v>282</v>
+        <v>379</v>
       </c>
       <c r="M118" t="s">
-        <v>283</v>
+        <v>121</v>
       </c>
     </row>
     <row r="119" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4131,33 +4134,30 @@
         <v>281</v>
       </c>
       <c r="C119" t="s">
-        <v>284</v>
+        <v>9</v>
       </c>
       <c r="L119" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="M119" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="120" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>71</v>
+        <v>292</v>
       </c>
       <c r="B120" t="s">
-        <v>74</v>
+        <v>281</v>
       </c>
       <c r="C120" t="s">
-        <v>9</v>
-      </c>
-      <c r="K120" t="s">
-        <v>39</v>
+        <v>284</v>
       </c>
       <c r="L120" t="s">
-        <v>74</v>
+        <v>285</v>
       </c>
       <c r="M120" t="s">
-        <v>121</v>
+        <v>286</v>
       </c>
     </row>
     <row r="121" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4165,7 +4165,7 @@
         <v>71</v>
       </c>
       <c r="B121" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C121" t="s">
         <v>9</v>
@@ -4174,7 +4174,7 @@
         <v>39</v>
       </c>
       <c r="L121" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M121" t="s">
         <v>121</v>
@@ -4185,7 +4185,7 @@
         <v>71</v>
       </c>
       <c r="B122" t="s">
-        <v>279</v>
+        <v>75</v>
       </c>
       <c r="C122" t="s">
         <v>9</v>
@@ -4194,7 +4194,7 @@
         <v>39</v>
       </c>
       <c r="L122" t="s">
-        <v>279</v>
+        <v>75</v>
       </c>
       <c r="M122" t="s">
         <v>121</v>
@@ -4205,16 +4205,19 @@
         <v>71</v>
       </c>
       <c r="B123" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C123" t="s">
         <v>9</v>
       </c>
+      <c r="K123" t="s">
+        <v>39</v>
+      </c>
       <c r="L123" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M123" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="124" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4222,16 +4225,16 @@
         <v>71</v>
       </c>
       <c r="B124" t="s">
-        <v>76</v>
+        <v>280</v>
       </c>
       <c r="C124" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="L124" t="s">
-        <v>76</v>
+        <v>280</v>
       </c>
       <c r="M124" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="125" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4239,16 +4242,13 @@
         <v>71</v>
       </c>
       <c r="B125" t="s">
-        <v>194</v>
+        <v>76</v>
       </c>
       <c r="C125" t="s">
         <v>15</v>
       </c>
-      <c r="H125" t="s">
-        <v>410</v>
-      </c>
       <c r="L125" t="s">
-        <v>194</v>
+        <v>76</v>
       </c>
       <c r="M125" t="s">
         <v>122</v>
@@ -4259,22 +4259,19 @@
         <v>71</v>
       </c>
       <c r="B126" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C126" t="s">
         <v>15</v>
       </c>
-      <c r="D126" t="s">
-        <v>331</v>
-      </c>
-      <c r="J126" t="s">
-        <v>426</v>
+      <c r="H126" t="s">
+        <v>410</v>
       </c>
       <c r="L126" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="M126" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="127" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4282,16 +4279,22 @@
         <v>71</v>
       </c>
       <c r="B127" t="s">
-        <v>374</v>
+        <v>201</v>
       </c>
       <c r="C127" t="s">
         <v>15</v>
       </c>
+      <c r="D127" t="s">
+        <v>331</v>
+      </c>
+      <c r="J127" t="s">
+        <v>426</v>
+      </c>
       <c r="L127" t="s">
-        <v>374</v>
+        <v>201</v>
       </c>
       <c r="M127" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="128" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4299,33 +4302,33 @@
         <v>71</v>
       </c>
       <c r="B128" t="s">
-        <v>266</v>
+        <v>374</v>
       </c>
       <c r="C128" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L128" t="s">
-        <v>266</v>
+        <v>374</v>
       </c>
       <c r="M128" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="129" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B129" t="s">
-        <v>78</v>
+        <v>266</v>
       </c>
       <c r="C129" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L129" t="s">
-        <v>78</v>
+        <v>266</v>
       </c>
       <c r="M129" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="130" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4333,28 +4336,16 @@
         <v>77</v>
       </c>
       <c r="B130" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C130" t="s">
         <v>9</v>
       </c>
-      <c r="D130" t="s">
-        <v>305</v>
-      </c>
-      <c r="F130" t="s">
-        <v>11</v>
-      </c>
-      <c r="H130" t="s">
-        <v>448</v>
-      </c>
-      <c r="I130" t="s">
-        <v>447</v>
-      </c>
       <c r="L130" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M130" t="s">
-        <v>149</v>
+        <v>120</v>
       </c>
     </row>
     <row r="131" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4362,22 +4353,28 @@
         <v>77</v>
       </c>
       <c r="B131" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C131" t="s">
         <v>9</v>
       </c>
       <c r="D131" t="s">
-        <v>322</v>
-      </c>
-      <c r="J131" t="s">
-        <v>427</v>
+        <v>305</v>
+      </c>
+      <c r="F131" t="s">
+        <v>11</v>
+      </c>
+      <c r="H131" t="s">
+        <v>448</v>
+      </c>
+      <c r="I131" t="s">
+        <v>447</v>
       </c>
       <c r="L131" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M131" t="s">
-        <v>121</v>
+        <v>149</v>
       </c>
     </row>
     <row r="132" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4385,13 +4382,19 @@
         <v>77</v>
       </c>
       <c r="B132" t="s">
-        <v>362</v>
+        <v>80</v>
       </c>
       <c r="C132" t="s">
-        <v>81</v>
+        <v>9</v>
+      </c>
+      <c r="D132" t="s">
+        <v>322</v>
+      </c>
+      <c r="J132" t="s">
+        <v>427</v>
       </c>
       <c r="L132" t="s">
-        <v>362</v>
+        <v>80</v>
       </c>
       <c r="M132" t="s">
         <v>121</v>
@@ -4402,13 +4405,13 @@
         <v>77</v>
       </c>
       <c r="B133" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C133" t="s">
         <v>81</v>
       </c>
       <c r="L133" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="M133" t="s">
         <v>121</v>
@@ -4419,16 +4422,16 @@
         <v>77</v>
       </c>
       <c r="B134" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C134" t="s">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="L134" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="M134" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="135" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4436,16 +4439,16 @@
         <v>77</v>
       </c>
       <c r="B135" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C135" t="s">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="L135" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="M135" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="136" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4453,16 +4456,16 @@
         <v>77</v>
       </c>
       <c r="B136" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C136" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="L136" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="M136" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="137" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4470,22 +4473,16 @@
         <v>77</v>
       </c>
       <c r="B137" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C137" t="s">
-        <v>15</v>
-      </c>
-      <c r="D137" t="s">
-        <v>323</v>
-      </c>
-      <c r="J137" t="s">
-        <v>428</v>
+        <v>9</v>
       </c>
       <c r="L137" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="M137" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="138" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4493,16 +4490,22 @@
         <v>77</v>
       </c>
       <c r="B138" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="C138" t="s">
         <v>15</v>
       </c>
+      <c r="D138" t="s">
+        <v>323</v>
+      </c>
+      <c r="J138" t="s">
+        <v>428</v>
+      </c>
       <c r="L138" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="M138" t="s">
-        <v>454</v>
+        <v>121</v>
       </c>
     </row>
     <row r="139" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4510,16 +4513,16 @@
         <v>77</v>
       </c>
       <c r="B139" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="C139" t="s">
         <v>15</v>
       </c>
       <c r="L139" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="M139" t="s">
-        <v>122</v>
+        <v>454</v>
       </c>
     </row>
     <row r="140" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4527,16 +4530,16 @@
         <v>77</v>
       </c>
       <c r="B140" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C140" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="L140" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="M140" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="141" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4544,22 +4547,16 @@
         <v>77</v>
       </c>
       <c r="B141" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C141" t="s">
-        <v>15</v>
-      </c>
-      <c r="D141" t="s">
-        <v>323</v>
-      </c>
-      <c r="J141" t="s">
-        <v>428</v>
+        <v>33</v>
       </c>
       <c r="L141" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="M141" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="142" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4567,47 +4564,53 @@
         <v>77</v>
       </c>
       <c r="B142" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="C142" t="s">
         <v>15</v>
       </c>
+      <c r="D142" t="s">
+        <v>323</v>
+      </c>
+      <c r="J142" t="s">
+        <v>428</v>
+      </c>
       <c r="L142" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="M142" t="s">
-        <v>454</v>
+        <v>121</v>
       </c>
     </row>
     <row r="143" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="B143" t="s">
-        <v>83</v>
+        <v>376</v>
       </c>
       <c r="C143" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L143" t="s">
-        <v>83</v>
+        <v>376</v>
       </c>
       <c r="M143" t="s">
-        <v>121</v>
+        <v>454</v>
       </c>
     </row>
     <row r="144" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="B144" t="s">
-        <v>371</v>
+        <v>83</v>
       </c>
       <c r="C144" t="s">
         <v>17</v>
       </c>
       <c r="L144" t="s">
-        <v>371</v>
+        <v>83</v>
       </c>
       <c r="M144" t="s">
         <v>121</v>
@@ -4618,13 +4621,13 @@
         <v>77</v>
       </c>
       <c r="B145" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C145" t="s">
         <v>17</v>
       </c>
       <c r="L145" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="M145" t="s">
         <v>121</v>
@@ -4635,19 +4638,16 @@
         <v>77</v>
       </c>
       <c r="B146" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C146" t="s">
-        <v>9</v>
-      </c>
-      <c r="K146" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L146" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="M146" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="147" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4655,16 +4655,19 @@
         <v>77</v>
       </c>
       <c r="B147" t="s">
-        <v>267</v>
+        <v>373</v>
       </c>
       <c r="C147" t="s">
-        <v>17</v>
+        <v>9</v>
+      </c>
+      <c r="K147" t="s">
+        <v>20</v>
       </c>
       <c r="L147" t="s">
-        <v>267</v>
+        <v>373</v>
       </c>
       <c r="M147" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="148" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4672,13 +4675,13 @@
         <v>77</v>
       </c>
       <c r="B148" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="C148" t="s">
         <v>17</v>
       </c>
       <c r="L148" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="M148" t="s">
         <v>121</v>
@@ -4686,16 +4689,16 @@
     </row>
     <row r="149" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="B149" t="s">
-        <v>84</v>
+        <v>261</v>
       </c>
       <c r="C149" t="s">
         <v>17</v>
       </c>
       <c r="L149" t="s">
-        <v>84</v>
+        <v>261</v>
       </c>
       <c r="M149" t="s">
         <v>121</v>
@@ -4703,22 +4706,16 @@
     </row>
     <row r="150" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="B150" t="s">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="C150" t="s">
-        <v>9</v>
-      </c>
-      <c r="D150" t="s">
-        <v>332</v>
-      </c>
-      <c r="J150" t="s">
-        <v>429</v>
+        <v>17</v>
       </c>
       <c r="L150" t="s">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="M150" t="s">
         <v>121</v>
@@ -4729,13 +4726,19 @@
         <v>77</v>
       </c>
       <c r="B151" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C151" t="s">
-        <v>17</v>
+        <v>9</v>
+      </c>
+      <c r="D151" t="s">
+        <v>332</v>
+      </c>
+      <c r="J151" t="s">
+        <v>429</v>
       </c>
       <c r="L151" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M151" t="s">
         <v>121</v>
@@ -4746,16 +4749,16 @@
         <v>77</v>
       </c>
       <c r="B152" t="s">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="C152" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="L152" t="s">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="M152" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4766,19 +4769,13 @@
         <v>85</v>
       </c>
       <c r="C153" t="s">
-        <v>15</v>
-      </c>
-      <c r="D153" t="s">
-        <v>308</v>
-      </c>
-      <c r="J153" t="s">
-        <v>438</v>
+        <v>33</v>
       </c>
       <c r="L153" t="s">
-        <v>237</v>
-      </c>
-      <c r="M153" s="1" t="s">
-        <v>244</v>
+        <v>85</v>
+      </c>
+      <c r="M153" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="154" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4786,19 +4783,22 @@
         <v>77</v>
       </c>
       <c r="B154" t="s">
-        <v>166</v>
+        <v>85</v>
       </c>
       <c r="C154" t="s">
         <v>15</v>
       </c>
-      <c r="H154" t="s">
-        <v>160</v>
+      <c r="D154" t="s">
+        <v>308</v>
+      </c>
+      <c r="J154" t="s">
+        <v>438</v>
       </c>
       <c r="L154" t="s">
-        <v>166</v>
-      </c>
-      <c r="M154" t="s">
-        <v>122</v>
+        <v>237</v>
+      </c>
+      <c r="M154" s="1" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="155" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4806,16 +4806,16 @@
         <v>77</v>
       </c>
       <c r="B155" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C155" t="s">
         <v>15</v>
       </c>
       <c r="H155" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L155" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M155" t="s">
         <v>122</v>
@@ -4826,16 +4826,16 @@
         <v>77</v>
       </c>
       <c r="B156" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="C156" t="s">
         <v>15</v>
       </c>
       <c r="H156" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="L156" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="M156" t="s">
         <v>122</v>
@@ -4846,19 +4846,19 @@
         <v>77</v>
       </c>
       <c r="B157" t="s">
-        <v>217</v>
+        <v>181</v>
       </c>
       <c r="C157" t="s">
         <v>15</v>
       </c>
       <c r="H157" t="s">
-        <v>219</v>
+        <v>159</v>
       </c>
       <c r="L157" t="s">
-        <v>217</v>
+        <v>181</v>
       </c>
       <c r="M157" t="s">
-        <v>218</v>
+        <v>122</v>
       </c>
     </row>
     <row r="158" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4866,16 +4866,19 @@
         <v>77</v>
       </c>
       <c r="B158" t="s">
-        <v>170</v>
+        <v>217</v>
       </c>
       <c r="C158" t="s">
-        <v>33</v>
+        <v>15</v>
+      </c>
+      <c r="H158" t="s">
+        <v>219</v>
       </c>
       <c r="L158" t="s">
-        <v>170</v>
+        <v>217</v>
       </c>
       <c r="M158" t="s">
-        <v>246</v>
+        <v>218</v>
       </c>
     </row>
     <row r="159" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4886,19 +4889,13 @@
         <v>170</v>
       </c>
       <c r="C159" t="s">
-        <v>15</v>
-      </c>
-      <c r="D159" t="s">
-        <v>308</v>
-      </c>
-      <c r="J159" t="s">
-        <v>438</v>
+        <v>33</v>
       </c>
       <c r="L159" t="s">
-        <v>236</v>
-      </c>
-      <c r="M159" s="1" t="s">
-        <v>244</v>
+        <v>170</v>
+      </c>
+      <c r="M159" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="160" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4906,16 +4903,22 @@
         <v>77</v>
       </c>
       <c r="B160" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C160" t="s">
-        <v>33</v>
+        <v>15</v>
+      </c>
+      <c r="D160" t="s">
+        <v>308</v>
+      </c>
+      <c r="J160" t="s">
+        <v>438</v>
       </c>
       <c r="L160" t="s">
-        <v>171</v>
-      </c>
-      <c r="M160" t="s">
-        <v>246</v>
+        <v>236</v>
+      </c>
+      <c r="M160" s="1" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="161" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4926,19 +4929,13 @@
         <v>171</v>
       </c>
       <c r="C161" t="s">
-        <v>15</v>
-      </c>
-      <c r="D161" t="s">
-        <v>308</v>
-      </c>
-      <c r="J161" t="s">
-        <v>438</v>
+        <v>33</v>
       </c>
       <c r="L161" t="s">
-        <v>235</v>
-      </c>
-      <c r="M161" s="1" t="s">
-        <v>244</v>
+        <v>171</v>
+      </c>
+      <c r="M161" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="162" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4946,16 +4943,22 @@
         <v>77</v>
       </c>
       <c r="B162" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="C162" t="s">
-        <v>9</v>
+        <v>15</v>
+      </c>
+      <c r="D162" t="s">
+        <v>308</v>
+      </c>
+      <c r="J162" t="s">
+        <v>438</v>
       </c>
       <c r="L162" t="s">
-        <v>158</v>
-      </c>
-      <c r="M162" t="s">
-        <v>125</v>
+        <v>235</v>
+      </c>
+      <c r="M162" s="1" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="163" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4963,19 +4966,16 @@
         <v>77</v>
       </c>
       <c r="B163" t="s">
-        <v>293</v>
+        <v>158</v>
       </c>
       <c r="C163" t="s">
-        <v>15</v>
-      </c>
-      <c r="H163" t="s">
-        <v>295</v>
+        <v>9</v>
       </c>
       <c r="L163" t="s">
-        <v>293</v>
+        <v>158</v>
       </c>
       <c r="M163" t="s">
-        <v>218</v>
+        <v>125</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4983,16 +4983,16 @@
         <v>77</v>
       </c>
       <c r="B164" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C164" t="s">
         <v>15</v>
       </c>
       <c r="H164" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L164" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M164" t="s">
         <v>218</v>
@@ -5003,16 +5003,16 @@
         <v>77</v>
       </c>
       <c r="B165" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C165" t="s">
         <v>15</v>
       </c>
       <c r="H165" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L165" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="M165" t="s">
         <v>218</v>
@@ -5023,16 +5023,19 @@
         <v>77</v>
       </c>
       <c r="B166" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C166" t="s">
-        <v>33</v>
+        <v>15</v>
+      </c>
+      <c r="H166" t="s">
+        <v>298</v>
       </c>
       <c r="L166" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="M166" t="s">
-        <v>246</v>
+        <v>218</v>
       </c>
     </row>
     <row r="167" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5043,19 +5046,13 @@
         <v>299</v>
       </c>
       <c r="C167" t="s">
-        <v>15</v>
-      </c>
-      <c r="D167" t="s">
-        <v>308</v>
-      </c>
-      <c r="J167" t="s">
-        <v>438</v>
+        <v>33</v>
       </c>
       <c r="L167" t="s">
-        <v>302</v>
-      </c>
-      <c r="M167" s="1" t="s">
-        <v>244</v>
+        <v>299</v>
+      </c>
+      <c r="M167" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="168" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5063,16 +5060,22 @@
         <v>77</v>
       </c>
       <c r="B168" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C168" t="s">
-        <v>33</v>
+        <v>15</v>
+      </c>
+      <c r="D168" t="s">
+        <v>308</v>
+      </c>
+      <c r="J168" t="s">
+        <v>438</v>
       </c>
       <c r="L168" t="s">
-        <v>300</v>
-      </c>
-      <c r="M168" t="s">
-        <v>246</v>
+        <v>302</v>
+      </c>
+      <c r="M168" s="1" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="169" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5083,19 +5086,13 @@
         <v>300</v>
       </c>
       <c r="C169" t="s">
-        <v>15</v>
-      </c>
-      <c r="D169" t="s">
-        <v>308</v>
-      </c>
-      <c r="J169" t="s">
-        <v>438</v>
+        <v>33</v>
       </c>
       <c r="L169" t="s">
-        <v>303</v>
-      </c>
-      <c r="M169" s="1" t="s">
-        <v>244</v>
+        <v>300</v>
+      </c>
+      <c r="M169" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="170" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5103,16 +5100,22 @@
         <v>77</v>
       </c>
       <c r="B170" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C170" t="s">
-        <v>9</v>
+        <v>15</v>
+      </c>
+      <c r="D170" t="s">
+        <v>308</v>
+      </c>
+      <c r="J170" t="s">
+        <v>438</v>
       </c>
       <c r="L170" t="s">
-        <v>301</v>
-      </c>
-      <c r="M170" t="s">
-        <v>125</v>
+        <v>303</v>
+      </c>
+      <c r="M170" s="1" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="171" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5120,19 +5123,16 @@
         <v>77</v>
       </c>
       <c r="B171" t="s">
-        <v>168</v>
+        <v>301</v>
       </c>
       <c r="C171" t="s">
-        <v>15</v>
-      </c>
-      <c r="H171" t="s">
-        <v>165</v>
+        <v>9</v>
       </c>
       <c r="L171" t="s">
-        <v>168</v>
+        <v>301</v>
       </c>
       <c r="M171" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="172" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5140,16 +5140,16 @@
         <v>77</v>
       </c>
       <c r="B172" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C172" t="s">
         <v>15</v>
       </c>
       <c r="H172" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L172" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="M172" t="s">
         <v>122</v>
@@ -5160,16 +5160,16 @@
         <v>77</v>
       </c>
       <c r="B173" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="C173" t="s">
         <v>15</v>
       </c>
       <c r="H173" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L173" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="M173" t="s">
         <v>122</v>
@@ -5180,19 +5180,19 @@
         <v>77</v>
       </c>
       <c r="B174" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="C174" t="s">
         <v>15</v>
       </c>
       <c r="H174" t="s">
-        <v>221</v>
+        <v>163</v>
       </c>
       <c r="L174" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="M174" t="s">
-        <v>218</v>
+        <v>122</v>
       </c>
     </row>
     <row r="175" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5200,16 +5200,19 @@
         <v>77</v>
       </c>
       <c r="B175" t="s">
-        <v>172</v>
+        <v>220</v>
       </c>
       <c r="C175" t="s">
-        <v>33</v>
+        <v>15</v>
+      </c>
+      <c r="H175" t="s">
+        <v>221</v>
       </c>
       <c r="L175" t="s">
-        <v>172</v>
+        <v>220</v>
       </c>
       <c r="M175" t="s">
-        <v>246</v>
+        <v>218</v>
       </c>
     </row>
     <row r="176" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5220,19 +5223,13 @@
         <v>172</v>
       </c>
       <c r="C176" t="s">
-        <v>15</v>
-      </c>
-      <c r="D176" t="s">
-        <v>308</v>
-      </c>
-      <c r="J176" t="s">
-        <v>438</v>
+        <v>33</v>
       </c>
       <c r="L176" t="s">
-        <v>234</v>
-      </c>
-      <c r="M176" s="1" t="s">
-        <v>244</v>
+        <v>172</v>
+      </c>
+      <c r="M176" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="177" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5240,16 +5237,22 @@
         <v>77</v>
       </c>
       <c r="B177" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C177" t="s">
-        <v>33</v>
+        <v>15</v>
+      </c>
+      <c r="D177" t="s">
+        <v>308</v>
+      </c>
+      <c r="J177" t="s">
+        <v>438</v>
       </c>
       <c r="L177" t="s">
-        <v>173</v>
-      </c>
-      <c r="M177" t="s">
-        <v>246</v>
+        <v>234</v>
+      </c>
+      <c r="M177" s="1" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="178" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5260,19 +5263,13 @@
         <v>173</v>
       </c>
       <c r="C178" t="s">
-        <v>15</v>
-      </c>
-      <c r="D178" t="s">
-        <v>308</v>
-      </c>
-      <c r="J178" t="s">
-        <v>438</v>
+        <v>33</v>
       </c>
       <c r="L178" t="s">
-        <v>233</v>
-      </c>
-      <c r="M178" s="1" t="s">
-        <v>244</v>
+        <v>173</v>
+      </c>
+      <c r="M178" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="179" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5280,16 +5277,22 @@
         <v>77</v>
       </c>
       <c r="B179" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C179" t="s">
-        <v>9</v>
+        <v>15</v>
+      </c>
+      <c r="D179" t="s">
+        <v>308</v>
+      </c>
+      <c r="J179" t="s">
+        <v>438</v>
       </c>
       <c r="L179" t="s">
-        <v>162</v>
-      </c>
-      <c r="M179" t="s">
-        <v>125</v>
+        <v>233</v>
+      </c>
+      <c r="M179" s="1" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="180" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5297,28 +5300,16 @@
         <v>77</v>
       </c>
       <c r="B180" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="C180" t="s">
         <v>9</v>
       </c>
-      <c r="D180" t="s">
-        <v>324</v>
-      </c>
-      <c r="E180" t="s">
-        <v>189</v>
-      </c>
-      <c r="F180" t="s">
-        <v>11</v>
-      </c>
-      <c r="G180" t="s">
-        <v>12</v>
-      </c>
       <c r="L180" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="M180" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="181" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5326,16 +5317,25 @@
         <v>77</v>
       </c>
       <c r="B181" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C181" t="s">
-        <v>81</v>
-      </c>
-      <c r="H181" t="s">
-        <v>186</v>
+        <v>9</v>
+      </c>
+      <c r="D181" t="s">
+        <v>324</v>
+      </c>
+      <c r="E181" t="s">
+        <v>189</v>
+      </c>
+      <c r="F181" t="s">
+        <v>11</v>
+      </c>
+      <c r="G181" t="s">
+        <v>12</v>
       </c>
       <c r="L181" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="M181" t="s">
         <v>121</v>
@@ -5346,16 +5346,16 @@
         <v>77</v>
       </c>
       <c r="B182" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C182" t="s">
         <v>81</v>
       </c>
       <c r="H182" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L182" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M182" t="s">
         <v>121</v>
@@ -5366,50 +5366,41 @@
         <v>77</v>
       </c>
       <c r="B183" t="s">
-        <v>404</v>
+        <v>185</v>
       </c>
       <c r="C183" t="s">
-        <v>9</v>
+        <v>81</v>
+      </c>
+      <c r="H183" t="s">
+        <v>187</v>
       </c>
       <c r="L183" t="s">
-        <v>404</v>
+        <v>185</v>
       </c>
       <c r="M183" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="184" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="B184" t="s">
-        <v>86</v>
+        <v>404</v>
       </c>
       <c r="C184" t="s">
         <v>9</v>
       </c>
-      <c r="D184" t="s">
-        <v>325</v>
-      </c>
-      <c r="E184" t="s">
-        <v>87</v>
-      </c>
-      <c r="F184" t="s">
-        <v>88</v>
-      </c>
-      <c r="G184" t="s">
-        <v>12</v>
-      </c>
       <c r="L184" t="s">
-        <v>86</v>
+        <v>404</v>
       </c>
       <c r="M184" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="185" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="B185" t="s">
         <v>86</v>
@@ -5420,14 +5411,14 @@
       <c r="D185" t="s">
         <v>325</v>
       </c>
+      <c r="E185" t="s">
+        <v>87</v>
+      </c>
       <c r="F185" t="s">
         <v>88</v>
       </c>
-      <c r="H185" t="s">
-        <v>269</v>
-      </c>
-      <c r="I185" t="s">
-        <v>270</v>
+      <c r="G185" t="s">
+        <v>12</v>
       </c>
       <c r="L185" t="s">
         <v>86</v>
@@ -5438,28 +5429,28 @@
     </row>
     <row r="186" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="B186" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C186" t="s">
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>326</v>
-      </c>
-      <c r="E186" t="s">
-        <v>90</v>
+        <v>325</v>
       </c>
       <c r="F186" t="s">
-        <v>11</v>
-      </c>
-      <c r="G186" t="s">
-        <v>12</v>
+        <v>88</v>
+      </c>
+      <c r="H186" t="s">
+        <v>269</v>
+      </c>
+      <c r="I186" t="s">
+        <v>270</v>
       </c>
       <c r="L186" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M186" t="s">
         <v>121</v>
@@ -5467,7 +5458,7 @@
     </row>
     <row r="187" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="B187" t="s">
         <v>89</v>
@@ -5478,14 +5469,14 @@
       <c r="D187" t="s">
         <v>326</v>
       </c>
+      <c r="E187" t="s">
+        <v>90</v>
+      </c>
       <c r="F187" t="s">
         <v>11</v>
       </c>
-      <c r="H187" t="s">
-        <v>271</v>
-      </c>
-      <c r="I187" t="s">
-        <v>272</v>
+      <c r="G187" t="s">
+        <v>12</v>
       </c>
       <c r="L187" t="s">
         <v>89</v>
@@ -5499,16 +5490,28 @@
         <v>77</v>
       </c>
       <c r="B188" t="s">
-        <v>179</v>
+        <v>89</v>
       </c>
       <c r="C188" t="s">
         <v>9</v>
       </c>
+      <c r="D188" t="s">
+        <v>326</v>
+      </c>
+      <c r="F188" t="s">
+        <v>11</v>
+      </c>
+      <c r="H188" t="s">
+        <v>271</v>
+      </c>
+      <c r="I188" t="s">
+        <v>272</v>
+      </c>
       <c r="L188" t="s">
-        <v>179</v>
+        <v>89</v>
       </c>
       <c r="M188" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="189" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5516,19 +5519,16 @@
         <v>77</v>
       </c>
       <c r="B189" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C189" t="s">
         <v>9</v>
       </c>
-      <c r="K189" t="s">
-        <v>39</v>
-      </c>
       <c r="L189" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M189" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="190" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5536,16 +5536,19 @@
         <v>77</v>
       </c>
       <c r="B190" t="s">
-        <v>129</v>
+        <v>177</v>
       </c>
       <c r="C190" t="s">
-        <v>52</v>
+        <v>9</v>
+      </c>
+      <c r="K190" t="s">
+        <v>39</v>
       </c>
       <c r="L190" t="s">
-        <v>129</v>
+        <v>177</v>
       </c>
       <c r="M190" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="191" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5556,19 +5559,13 @@
         <v>129</v>
       </c>
       <c r="C191" t="s">
-        <v>15</v>
-      </c>
-      <c r="D191" t="s">
-        <v>308</v>
-      </c>
-      <c r="J191" t="s">
-        <v>438</v>
+        <v>52</v>
       </c>
       <c r="L191" t="s">
-        <v>232</v>
-      </c>
-      <c r="M191" s="1" t="s">
-        <v>245</v>
+        <v>129</v>
+      </c>
+      <c r="M191" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="192" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5576,19 +5573,22 @@
         <v>77</v>
       </c>
       <c r="B192" t="s">
-        <v>455</v>
+        <v>129</v>
       </c>
       <c r="C192" t="s">
-        <v>9</v>
-      </c>
-      <c r="K192" t="s">
-        <v>114</v>
+        <v>15</v>
+      </c>
+      <c r="D192" t="s">
+        <v>308</v>
+      </c>
+      <c r="J192" t="s">
+        <v>438</v>
       </c>
       <c r="L192" t="s">
-        <v>455</v>
-      </c>
-      <c r="M192" t="s">
-        <v>121</v>
+        <v>232</v>
+      </c>
+      <c r="M192" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="193" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5596,19 +5596,19 @@
         <v>77</v>
       </c>
       <c r="B193" t="s">
-        <v>133</v>
+        <v>455</v>
       </c>
       <c r="C193" t="s">
-        <v>15</v>
-      </c>
-      <c r="H193" t="s">
-        <v>132</v>
+        <v>9</v>
+      </c>
+      <c r="K193" t="s">
+        <v>114</v>
       </c>
       <c r="L193" t="s">
-        <v>133</v>
+        <v>455</v>
       </c>
       <c r="M193" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="194" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5616,16 +5616,19 @@
         <v>77</v>
       </c>
       <c r="B194" t="s">
-        <v>91</v>
+        <v>133</v>
       </c>
       <c r="C194" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+      <c r="H194" t="s">
+        <v>132</v>
       </c>
       <c r="L194" t="s">
-        <v>91</v>
+        <v>133</v>
       </c>
       <c r="M194" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="195" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5633,16 +5636,16 @@
         <v>77</v>
       </c>
       <c r="B195" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C195" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L195" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M195" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="196" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5650,13 +5653,13 @@
         <v>77</v>
       </c>
       <c r="B196" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C196" t="s">
-        <v>94</v>
+        <v>9</v>
       </c>
       <c r="L196" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M196" t="s">
         <v>127</v>
@@ -5667,13 +5670,13 @@
         <v>77</v>
       </c>
       <c r="B197" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C197" t="s">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="L197" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="M197" t="s">
         <v>127</v>
@@ -5687,19 +5690,13 @@
         <v>95</v>
       </c>
       <c r="C198" t="s">
-        <v>15</v>
-      </c>
-      <c r="D198" t="s">
-        <v>308</v>
-      </c>
-      <c r="J198" t="s">
-        <v>438</v>
+        <v>33</v>
       </c>
       <c r="L198" t="s">
-        <v>231</v>
-      </c>
-      <c r="M198" s="1" t="s">
-        <v>244</v>
+        <v>95</v>
+      </c>
+      <c r="M198" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="199" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5707,16 +5704,22 @@
         <v>77</v>
       </c>
       <c r="B199" t="s">
-        <v>192</v>
+        <v>95</v>
       </c>
       <c r="C199" t="s">
-        <v>52</v>
+        <v>15</v>
+      </c>
+      <c r="D199" t="s">
+        <v>308</v>
+      </c>
+      <c r="J199" t="s">
+        <v>438</v>
       </c>
       <c r="L199" t="s">
-        <v>192</v>
-      </c>
-      <c r="M199" t="s">
-        <v>127</v>
+        <v>231</v>
+      </c>
+      <c r="M199" s="1" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="200" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5727,19 +5730,13 @@
         <v>192</v>
       </c>
       <c r="C200" t="s">
-        <v>15</v>
-      </c>
-      <c r="D200" t="s">
-        <v>308</v>
-      </c>
-      <c r="J200" t="s">
-        <v>438</v>
+        <v>52</v>
       </c>
       <c r="L200" t="s">
-        <v>230</v>
-      </c>
-      <c r="M200" s="1" t="s">
-        <v>245</v>
+        <v>192</v>
+      </c>
+      <c r="M200" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="201" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5747,16 +5744,22 @@
         <v>77</v>
       </c>
       <c r="B201" t="s">
-        <v>287</v>
+        <v>192</v>
       </c>
       <c r="C201" t="s">
-        <v>284</v>
+        <v>15</v>
+      </c>
+      <c r="D201" t="s">
+        <v>308</v>
+      </c>
+      <c r="J201" t="s">
+        <v>438</v>
       </c>
       <c r="L201" t="s">
-        <v>287</v>
-      </c>
-      <c r="M201" t="s">
-        <v>127</v>
+        <v>230</v>
+      </c>
+      <c r="M201" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="202" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5767,47 +5770,35 @@
         <v>287</v>
       </c>
       <c r="C202" t="s">
-        <v>9</v>
+        <v>284</v>
       </c>
       <c r="L202" t="s">
-        <v>288</v>
-      </c>
-      <c r="M202" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
+      </c>
+      <c r="M202" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="203" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="B203" t="s">
-        <v>96</v>
+        <v>287</v>
       </c>
       <c r="C203" t="s">
         <v>9</v>
       </c>
-      <c r="D203" t="s">
-        <v>327</v>
-      </c>
-      <c r="E203" t="s">
-        <v>97</v>
-      </c>
-      <c r="F203" t="s">
-        <v>88</v>
-      </c>
-      <c r="G203" t="s">
-        <v>12</v>
-      </c>
       <c r="L203" t="s">
-        <v>96</v>
-      </c>
-      <c r="M203" t="s">
-        <v>121</v>
+        <v>288</v>
+      </c>
+      <c r="M203" s="1" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="204" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="B204" t="s">
         <v>96</v>
@@ -5818,14 +5809,14 @@
       <c r="D204" t="s">
         <v>327</v>
       </c>
+      <c r="E204" t="s">
+        <v>97</v>
+      </c>
       <c r="F204" t="s">
         <v>88</v>
       </c>
-      <c r="H204" t="s">
-        <v>273</v>
-      </c>
-      <c r="I204" t="s">
-        <v>274</v>
+      <c r="G204" t="s">
+        <v>12</v>
       </c>
       <c r="L204" t="s">
         <v>96</v>
@@ -5839,19 +5830,28 @@
         <v>77</v>
       </c>
       <c r="B205" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="C205" t="s">
-        <v>15</v>
+        <v>9</v>
+      </c>
+      <c r="D205" t="s">
+        <v>327</v>
+      </c>
+      <c r="F205" t="s">
+        <v>88</v>
       </c>
       <c r="H205" t="s">
-        <v>410</v>
+        <v>273</v>
+      </c>
+      <c r="I205" t="s">
+        <v>274</v>
       </c>
       <c r="L205" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="M205" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="206" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5859,50 +5859,41 @@
         <v>77</v>
       </c>
       <c r="B206" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C206" t="s">
-        <v>9</v>
+        <v>15</v>
+      </c>
+      <c r="H206" t="s">
+        <v>410</v>
       </c>
       <c r="L206" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="M206" t="s">
-        <v>449</v>
+        <v>122</v>
       </c>
     </row>
     <row r="207" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="B207" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="C207" t="s">
         <v>9</v>
       </c>
-      <c r="D207" t="s">
-        <v>328</v>
-      </c>
-      <c r="E207" t="s">
-        <v>99</v>
-      </c>
-      <c r="F207" t="s">
-        <v>88</v>
-      </c>
-      <c r="G207" t="s">
-        <v>12</v>
-      </c>
       <c r="L207" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="M207" t="s">
-        <v>121</v>
+        <v>449</v>
       </c>
     </row>
     <row r="208" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="B208" t="s">
         <v>98</v>
@@ -5913,14 +5904,14 @@
       <c r="D208" t="s">
         <v>328</v>
       </c>
+      <c r="E208" t="s">
+        <v>99</v>
+      </c>
       <c r="F208" t="s">
         <v>88</v>
       </c>
-      <c r="H208" t="s">
-        <v>275</v>
-      </c>
-      <c r="I208" t="s">
-        <v>276</v>
+      <c r="G208" t="s">
+        <v>12</v>
       </c>
       <c r="L208" t="s">
         <v>98</v>
@@ -5931,28 +5922,28 @@
     </row>
     <row r="209" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="B209" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C209" t="s">
         <v>9</v>
       </c>
       <c r="D209" t="s">
-        <v>326</v>
-      </c>
-      <c r="E209" t="s">
-        <v>101</v>
+        <v>328</v>
       </c>
       <c r="F209" t="s">
-        <v>11</v>
-      </c>
-      <c r="G209" t="s">
-        <v>12</v>
+        <v>88</v>
+      </c>
+      <c r="H209" t="s">
+        <v>275</v>
+      </c>
+      <c r="I209" t="s">
+        <v>276</v>
       </c>
       <c r="L209" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M209" t="s">
         <v>121</v>
@@ -5960,7 +5951,7 @@
     </row>
     <row r="210" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="B210" t="s">
         <v>100</v>
@@ -5971,14 +5962,14 @@
       <c r="D210" t="s">
         <v>326</v>
       </c>
+      <c r="E210" t="s">
+        <v>101</v>
+      </c>
       <c r="F210" t="s">
         <v>11</v>
       </c>
-      <c r="H210" t="s">
-        <v>277</v>
-      </c>
-      <c r="I210" t="s">
-        <v>272</v>
+      <c r="G210" t="s">
+        <v>12</v>
       </c>
       <c r="L210" t="s">
         <v>100</v>
@@ -5992,53 +5983,65 @@
         <v>77</v>
       </c>
       <c r="B211" t="s">
-        <v>178</v>
+        <v>100</v>
       </c>
       <c r="C211" t="s">
         <v>9</v>
       </c>
+      <c r="D211" t="s">
+        <v>326</v>
+      </c>
+      <c r="F211" t="s">
+        <v>11</v>
+      </c>
+      <c r="H211" t="s">
+        <v>277</v>
+      </c>
+      <c r="I211" t="s">
+        <v>272</v>
+      </c>
       <c r="L211" t="s">
-        <v>178</v>
+        <v>100</v>
       </c>
       <c r="M211" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="212" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="B212" t="s">
-        <v>112</v>
+        <v>178</v>
       </c>
       <c r="C212" t="s">
         <v>9</v>
       </c>
-      <c r="K212" t="s">
-        <v>39</v>
-      </c>
       <c r="L212" t="s">
-        <v>112</v>
+        <v>178</v>
       </c>
       <c r="M212" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="213" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="B213" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="C213" t="s">
-        <v>52</v>
+        <v>9</v>
+      </c>
+      <c r="K213" t="s">
+        <v>39</v>
       </c>
       <c r="L213" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="M213" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="214" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6049,19 +6052,13 @@
         <v>130</v>
       </c>
       <c r="C214" t="s">
-        <v>15</v>
-      </c>
-      <c r="D214" t="s">
-        <v>308</v>
-      </c>
-      <c r="J214" t="s">
-        <v>438</v>
+        <v>52</v>
       </c>
       <c r="L214" t="s">
-        <v>229</v>
-      </c>
-      <c r="M214" s="1" t="s">
-        <v>245</v>
+        <v>130</v>
+      </c>
+      <c r="M214" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="215" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6069,19 +6066,22 @@
         <v>77</v>
       </c>
       <c r="B215" t="s">
-        <v>456</v>
+        <v>130</v>
       </c>
       <c r="C215" t="s">
-        <v>9</v>
-      </c>
-      <c r="K215" t="s">
-        <v>114</v>
+        <v>15</v>
+      </c>
+      <c r="D215" t="s">
+        <v>308</v>
+      </c>
+      <c r="J215" t="s">
+        <v>438</v>
       </c>
       <c r="L215" t="s">
-        <v>456</v>
-      </c>
-      <c r="M215" t="s">
-        <v>121</v>
+        <v>229</v>
+      </c>
+      <c r="M215" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="216" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6089,19 +6089,19 @@
         <v>77</v>
       </c>
       <c r="B216" t="s">
-        <v>134</v>
+        <v>456</v>
       </c>
       <c r="C216" t="s">
-        <v>15</v>
-      </c>
-      <c r="H216" t="s">
-        <v>132</v>
+        <v>9</v>
+      </c>
+      <c r="K216" t="s">
+        <v>114</v>
       </c>
       <c r="L216" t="s">
-        <v>134</v>
+        <v>456</v>
       </c>
       <c r="M216" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="217" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6109,16 +6109,19 @@
         <v>77</v>
       </c>
       <c r="B217" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="C217" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+      <c r="H217" t="s">
+        <v>132</v>
       </c>
       <c r="L217" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="M217" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="218" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6126,16 +6129,16 @@
         <v>77</v>
       </c>
       <c r="B218" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C218" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L218" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M218" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="219" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6143,13 +6146,13 @@
         <v>77</v>
       </c>
       <c r="B219" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C219" t="s">
-        <v>94</v>
+        <v>9</v>
       </c>
       <c r="L219" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M219" t="s">
         <v>127</v>
@@ -6160,13 +6163,13 @@
         <v>77</v>
       </c>
       <c r="B220" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C220" t="s">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="L220" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M220" t="s">
         <v>127</v>
@@ -6180,19 +6183,13 @@
         <v>105</v>
       </c>
       <c r="C221" t="s">
-        <v>15</v>
-      </c>
-      <c r="D221" t="s">
-        <v>308</v>
-      </c>
-      <c r="J221" t="s">
-        <v>438</v>
+        <v>33</v>
       </c>
       <c r="L221" t="s">
-        <v>228</v>
-      </c>
-      <c r="M221" s="1" t="s">
-        <v>244</v>
+        <v>105</v>
+      </c>
+      <c r="M221" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="222" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6200,16 +6197,22 @@
         <v>77</v>
       </c>
       <c r="B222" t="s">
-        <v>191</v>
+        <v>105</v>
       </c>
       <c r="C222" t="s">
-        <v>52</v>
+        <v>15</v>
+      </c>
+      <c r="D222" t="s">
+        <v>308</v>
+      </c>
+      <c r="J222" t="s">
+        <v>438</v>
       </c>
       <c r="L222" t="s">
-        <v>191</v>
-      </c>
-      <c r="M222" t="s">
-        <v>127</v>
+        <v>228</v>
+      </c>
+      <c r="M222" s="1" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="223" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6220,19 +6223,13 @@
         <v>191</v>
       </c>
       <c r="C223" t="s">
-        <v>15</v>
-      </c>
-      <c r="D223" t="s">
-        <v>308</v>
-      </c>
-      <c r="J223" t="s">
-        <v>438</v>
+        <v>52</v>
       </c>
       <c r="L223" t="s">
-        <v>227</v>
-      </c>
-      <c r="M223" s="1" t="s">
-        <v>245</v>
+        <v>191</v>
+      </c>
+      <c r="M223" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="224" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6240,16 +6237,22 @@
         <v>77</v>
       </c>
       <c r="B224" t="s">
-        <v>290</v>
+        <v>191</v>
       </c>
       <c r="C224" t="s">
-        <v>284</v>
+        <v>15</v>
+      </c>
+      <c r="D224" t="s">
+        <v>308</v>
+      </c>
+      <c r="J224" t="s">
+        <v>438</v>
       </c>
       <c r="L224" t="s">
-        <v>290</v>
-      </c>
-      <c r="M224" t="s">
-        <v>127</v>
+        <v>227</v>
+      </c>
+      <c r="M224" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="225" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6260,47 +6263,35 @@
         <v>290</v>
       </c>
       <c r="C225" t="s">
-        <v>9</v>
+        <v>284</v>
       </c>
       <c r="L225" t="s">
-        <v>291</v>
-      </c>
-      <c r="M225" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
+      </c>
+      <c r="M225" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="226" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="B226" t="s">
-        <v>106</v>
+        <v>290</v>
       </c>
       <c r="C226" t="s">
         <v>9</v>
       </c>
-      <c r="D226" t="s">
-        <v>327</v>
-      </c>
-      <c r="E226" t="s">
-        <v>107</v>
-      </c>
-      <c r="F226" t="s">
-        <v>88</v>
-      </c>
-      <c r="G226" t="s">
-        <v>12</v>
-      </c>
       <c r="L226" t="s">
-        <v>106</v>
-      </c>
-      <c r="M226" t="s">
-        <v>121</v>
+        <v>291</v>
+      </c>
+      <c r="M226" s="1" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="227" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="B227" t="s">
         <v>106</v>
@@ -6311,14 +6302,14 @@
       <c r="D227" t="s">
         <v>327</v>
       </c>
+      <c r="E227" t="s">
+        <v>107</v>
+      </c>
       <c r="F227" t="s">
         <v>88</v>
       </c>
-      <c r="H227" t="s">
-        <v>278</v>
-      </c>
-      <c r="I227" t="s">
-        <v>274</v>
+      <c r="G227" t="s">
+        <v>12</v>
       </c>
       <c r="L227" t="s">
         <v>106</v>
@@ -6332,19 +6323,28 @@
         <v>77</v>
       </c>
       <c r="B228" t="s">
-        <v>142</v>
+        <v>106</v>
       </c>
       <c r="C228" t="s">
-        <v>15</v>
+        <v>9</v>
+      </c>
+      <c r="D228" t="s">
+        <v>327</v>
+      </c>
+      <c r="F228" t="s">
+        <v>88</v>
       </c>
       <c r="H228" t="s">
-        <v>410</v>
+        <v>278</v>
+      </c>
+      <c r="I228" t="s">
+        <v>274</v>
       </c>
       <c r="L228" t="s">
-        <v>142</v>
+        <v>106</v>
       </c>
       <c r="M228" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="229" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6352,16 +6352,19 @@
         <v>77</v>
       </c>
       <c r="B229" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C229" t="s">
-        <v>9</v>
+        <v>15</v>
+      </c>
+      <c r="H229" t="s">
+        <v>410</v>
       </c>
       <c r="L229" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="M229" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="230" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6369,16 +6372,16 @@
         <v>77</v>
       </c>
       <c r="B230" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="C230" t="s">
-        <v>81</v>
+        <v>9</v>
       </c>
       <c r="L230" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="M230" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="231" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6386,25 +6389,13 @@
         <v>77</v>
       </c>
       <c r="B231" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C231" t="s">
-        <v>9</v>
-      </c>
-      <c r="D231" t="s">
-        <v>333</v>
-      </c>
-      <c r="E231" t="s">
-        <v>110</v>
-      </c>
-      <c r="F231" t="s">
-        <v>11</v>
-      </c>
-      <c r="G231" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="L231" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M231" t="s">
         <v>121</v>
@@ -6415,50 +6406,50 @@
         <v>77</v>
       </c>
       <c r="B232" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C232" t="s">
         <v>9</v>
       </c>
+      <c r="D232" t="s">
+        <v>333</v>
+      </c>
+      <c r="E232" t="s">
+        <v>110</v>
+      </c>
+      <c r="F232" t="s">
+        <v>11</v>
+      </c>
+      <c r="G232" t="s">
+        <v>12</v>
+      </c>
       <c r="L232" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="M232" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="233" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="B233" t="s">
-        <v>334</v>
+        <v>111</v>
       </c>
       <c r="C233" t="s">
         <v>9</v>
       </c>
-      <c r="D233" t="s">
-        <v>335</v>
-      </c>
-      <c r="E233" t="s">
-        <v>336</v>
-      </c>
-      <c r="F233" t="s">
-        <v>88</v>
-      </c>
-      <c r="G233" t="s">
-        <v>12</v>
-      </c>
       <c r="L233" t="s">
-        <v>334</v>
+        <v>111</v>
       </c>
       <c r="M233" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="234" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="B234" t="s">
         <v>334</v>
@@ -6469,14 +6460,14 @@
       <c r="D234" t="s">
         <v>335</v>
       </c>
+      <c r="E234" t="s">
+        <v>336</v>
+      </c>
       <c r="F234" t="s">
         <v>88</v>
       </c>
-      <c r="H234" t="s">
-        <v>337</v>
-      </c>
-      <c r="I234" t="s">
-        <v>338</v>
+      <c r="G234" t="s">
+        <v>12</v>
       </c>
       <c r="L234" t="s">
         <v>334</v>
@@ -6487,28 +6478,28 @@
     </row>
     <row r="235" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="B235" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="C235" t="s">
         <v>9</v>
       </c>
       <c r="D235" t="s">
-        <v>326</v>
-      </c>
-      <c r="E235" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="F235" t="s">
-        <v>11</v>
-      </c>
-      <c r="G235" t="s">
-        <v>12</v>
+        <v>88</v>
+      </c>
+      <c r="H235" t="s">
+        <v>337</v>
+      </c>
+      <c r="I235" t="s">
+        <v>338</v>
       </c>
       <c r="L235" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="M235" t="s">
         <v>121</v>
@@ -6516,7 +6507,7 @@
     </row>
     <row r="236" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="B236" t="s">
         <v>339</v>
@@ -6527,14 +6518,14 @@
       <c r="D236" t="s">
         <v>326</v>
       </c>
+      <c r="E236" t="s">
+        <v>340</v>
+      </c>
       <c r="F236" t="s">
         <v>11</v>
       </c>
-      <c r="H236" t="s">
-        <v>341</v>
-      </c>
-      <c r="I236" t="s">
-        <v>272</v>
+      <c r="G236" t="s">
+        <v>12</v>
       </c>
       <c r="L236" t="s">
         <v>339</v>
@@ -6548,53 +6539,65 @@
         <v>77</v>
       </c>
       <c r="B237" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C237" t="s">
         <v>9</v>
       </c>
+      <c r="D237" t="s">
+        <v>326</v>
+      </c>
+      <c r="F237" t="s">
+        <v>11</v>
+      </c>
+      <c r="H237" t="s">
+        <v>341</v>
+      </c>
+      <c r="I237" t="s">
+        <v>272</v>
+      </c>
       <c r="L237" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="M237" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="238" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="B238" t="s">
-        <v>112</v>
+        <v>342</v>
       </c>
       <c r="C238" t="s">
         <v>9</v>
       </c>
-      <c r="K238" t="s">
-        <v>39</v>
-      </c>
       <c r="L238" t="s">
-        <v>112</v>
+        <v>342</v>
       </c>
       <c r="M238" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="239" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="B239" t="s">
-        <v>343</v>
+        <v>112</v>
       </c>
       <c r="C239" t="s">
-        <v>52</v>
+        <v>9</v>
+      </c>
+      <c r="K239" t="s">
+        <v>39</v>
       </c>
       <c r="L239" t="s">
-        <v>343</v>
+        <v>112</v>
       </c>
       <c r="M239" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="240" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6605,19 +6608,13 @@
         <v>343</v>
       </c>
       <c r="C240" t="s">
-        <v>15</v>
-      </c>
-      <c r="D240" t="s">
-        <v>308</v>
-      </c>
-      <c r="J240" t="s">
-        <v>438</v>
+        <v>52</v>
       </c>
       <c r="L240" t="s">
-        <v>344</v>
-      </c>
-      <c r="M240" s="1" t="s">
-        <v>245</v>
+        <v>343</v>
+      </c>
+      <c r="M240" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="241" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6625,19 +6622,22 @@
         <v>77</v>
       </c>
       <c r="B241" t="s">
-        <v>457</v>
+        <v>343</v>
       </c>
       <c r="C241" t="s">
-        <v>9</v>
-      </c>
-      <c r="K241" t="s">
-        <v>114</v>
+        <v>15</v>
+      </c>
+      <c r="D241" t="s">
+        <v>308</v>
+      </c>
+      <c r="J241" t="s">
+        <v>438</v>
       </c>
       <c r="L241" t="s">
-        <v>457</v>
-      </c>
-      <c r="M241" t="s">
-        <v>121</v>
+        <v>344</v>
+      </c>
+      <c r="M241" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="242" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6645,19 +6645,19 @@
         <v>77</v>
       </c>
       <c r="B242" t="s">
-        <v>345</v>
+        <v>457</v>
       </c>
       <c r="C242" t="s">
-        <v>15</v>
-      </c>
-      <c r="H242" t="s">
-        <v>132</v>
+        <v>9</v>
+      </c>
+      <c r="K242" t="s">
+        <v>114</v>
       </c>
       <c r="L242" t="s">
-        <v>345</v>
+        <v>457</v>
       </c>
       <c r="M242" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="243" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6665,16 +6665,19 @@
         <v>77</v>
       </c>
       <c r="B243" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C243" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+      <c r="H243" t="s">
+        <v>132</v>
       </c>
       <c r="L243" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="M243" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="244" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6682,16 +6685,16 @@
         <v>77</v>
       </c>
       <c r="B244" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C244" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L244" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M244" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="245" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6699,13 +6702,13 @@
         <v>77</v>
       </c>
       <c r="B245" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C245" t="s">
-        <v>94</v>
+        <v>9</v>
       </c>
       <c r="L245" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="M245" t="s">
         <v>127</v>
@@ -6716,13 +6719,13 @@
         <v>77</v>
       </c>
       <c r="B246" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C246" t="s">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="L246" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M246" t="s">
         <v>127</v>
@@ -6736,19 +6739,13 @@
         <v>349</v>
       </c>
       <c r="C247" t="s">
-        <v>15</v>
-      </c>
-      <c r="D247" t="s">
-        <v>308</v>
-      </c>
-      <c r="J247" t="s">
-        <v>438</v>
+        <v>33</v>
       </c>
       <c r="L247" t="s">
-        <v>350</v>
-      </c>
-      <c r="M247" s="1" t="s">
-        <v>244</v>
+        <v>349</v>
+      </c>
+      <c r="M247" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="248" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6756,16 +6753,22 @@
         <v>77</v>
       </c>
       <c r="B248" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C248" t="s">
-        <v>52</v>
+        <v>15</v>
+      </c>
+      <c r="D248" t="s">
+        <v>308</v>
+      </c>
+      <c r="J248" t="s">
+        <v>438</v>
       </c>
       <c r="L248" t="s">
-        <v>351</v>
-      </c>
-      <c r="M248" t="s">
-        <v>127</v>
+        <v>350</v>
+      </c>
+      <c r="M248" s="1" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="249" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6776,19 +6779,13 @@
         <v>351</v>
       </c>
       <c r="C249" t="s">
-        <v>15</v>
-      </c>
-      <c r="D249" t="s">
-        <v>308</v>
-      </c>
-      <c r="J249" t="s">
-        <v>438</v>
+        <v>52</v>
       </c>
       <c r="L249" t="s">
-        <v>352</v>
-      </c>
-      <c r="M249" s="1" t="s">
-        <v>245</v>
+        <v>351</v>
+      </c>
+      <c r="M249" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="250" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6796,16 +6793,22 @@
         <v>77</v>
       </c>
       <c r="B250" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C250" t="s">
-        <v>284</v>
+        <v>15</v>
+      </c>
+      <c r="D250" t="s">
+        <v>308</v>
+      </c>
+      <c r="J250" t="s">
+        <v>438</v>
       </c>
       <c r="L250" t="s">
-        <v>353</v>
-      </c>
-      <c r="M250" t="s">
-        <v>127</v>
+        <v>352</v>
+      </c>
+      <c r="M250" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="251" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6816,47 +6819,35 @@
         <v>353</v>
       </c>
       <c r="C251" t="s">
-        <v>9</v>
+        <v>284</v>
       </c>
       <c r="L251" t="s">
-        <v>354</v>
-      </c>
-      <c r="M251" s="1" t="s">
-        <v>289</v>
+        <v>353</v>
+      </c>
+      <c r="M251" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="252" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="B252" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C252" t="s">
         <v>9</v>
       </c>
-      <c r="D252" t="s">
-        <v>327</v>
-      </c>
-      <c r="E252" t="s">
-        <v>358</v>
-      </c>
-      <c r="F252" t="s">
-        <v>88</v>
-      </c>
-      <c r="G252" t="s">
-        <v>12</v>
-      </c>
       <c r="L252" t="s">
-        <v>355</v>
-      </c>
-      <c r="M252" t="s">
-        <v>121</v>
+        <v>354</v>
+      </c>
+      <c r="M252" s="1" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="253" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="B253" t="s">
         <v>355</v>
@@ -6867,14 +6858,14 @@
       <c r="D253" t="s">
         <v>327</v>
       </c>
+      <c r="E253" t="s">
+        <v>358</v>
+      </c>
       <c r="F253" t="s">
         <v>88</v>
       </c>
-      <c r="H253" t="s">
-        <v>359</v>
-      </c>
-      <c r="I253" t="s">
-        <v>274</v>
+      <c r="G253" t="s">
+        <v>12</v>
       </c>
       <c r="L253" t="s">
         <v>355</v>
@@ -6888,19 +6879,28 @@
         <v>77</v>
       </c>
       <c r="B254" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C254" t="s">
-        <v>15</v>
+        <v>9</v>
+      </c>
+      <c r="D254" t="s">
+        <v>327</v>
+      </c>
+      <c r="F254" t="s">
+        <v>88</v>
       </c>
       <c r="H254" t="s">
-        <v>410</v>
+        <v>359</v>
+      </c>
+      <c r="I254" t="s">
+        <v>274</v>
       </c>
       <c r="L254" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="M254" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="255" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6908,16 +6908,19 @@
         <v>77</v>
       </c>
       <c r="B255" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C255" t="s">
-        <v>9</v>
+        <v>15</v>
+      </c>
+      <c r="H255" t="s">
+        <v>410</v>
       </c>
       <c r="L255" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="M255" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="256" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6925,16 +6928,16 @@
         <v>77</v>
       </c>
       <c r="B256" t="s">
-        <v>150</v>
+        <v>357</v>
       </c>
       <c r="C256" t="s">
-        <v>81</v>
+        <v>9</v>
       </c>
       <c r="L256" t="s">
-        <v>150</v>
+        <v>357</v>
       </c>
       <c r="M256" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="257" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6942,19 +6945,13 @@
         <v>77</v>
       </c>
       <c r="B257" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C257" t="s">
-        <v>9</v>
-      </c>
-      <c r="D257" t="s">
-        <v>314</v>
-      </c>
-      <c r="J257" t="s">
-        <v>430</v>
+        <v>81</v>
       </c>
       <c r="L257" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M257" t="s">
         <v>121</v>
@@ -6965,16 +6962,22 @@
         <v>77</v>
       </c>
       <c r="B258" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C258" t="s">
         <v>9</v>
       </c>
+      <c r="D258" t="s">
+        <v>314</v>
+      </c>
+      <c r="J258" t="s">
+        <v>430</v>
+      </c>
       <c r="L258" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M258" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="259" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6982,16 +6985,16 @@
         <v>77</v>
       </c>
       <c r="B259" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C259" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="L259" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M259" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="260" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6999,16 +7002,13 @@
         <v>77</v>
       </c>
       <c r="B260" t="s">
-        <v>405</v>
+        <v>153</v>
       </c>
       <c r="C260" t="s">
-        <v>9</v>
-      </c>
-      <c r="K260" t="s">
-        <v>385</v>
+        <v>17</v>
       </c>
       <c r="L260" t="s">
-        <v>405</v>
+        <v>153</v>
       </c>
       <c r="M260" t="s">
         <v>121</v>
@@ -7019,16 +7019,16 @@
         <v>77</v>
       </c>
       <c r="B261" t="s">
-        <v>112</v>
+        <v>405</v>
       </c>
       <c r="C261" t="s">
         <v>9</v>
       </c>
       <c r="K261" t="s">
-        <v>39</v>
+        <v>385</v>
       </c>
       <c r="L261" t="s">
-        <v>112</v>
+        <v>405</v>
       </c>
       <c r="M261" t="s">
         <v>121</v>
@@ -7039,16 +7039,16 @@
         <v>77</v>
       </c>
       <c r="B262" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C262" t="s">
         <v>9</v>
       </c>
-      <c r="J262" t="s">
-        <v>431</v>
+      <c r="K262" t="s">
+        <v>39</v>
       </c>
       <c r="L262" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M262" t="s">
         <v>121</v>
@@ -7059,16 +7059,19 @@
         <v>77</v>
       </c>
       <c r="B263" t="s">
-        <v>206</v>
+        <v>113</v>
       </c>
       <c r="C263" t="s">
-        <v>52</v>
+        <v>9</v>
+      </c>
+      <c r="J263" t="s">
+        <v>431</v>
       </c>
       <c r="L263" t="s">
-        <v>206</v>
+        <v>113</v>
       </c>
       <c r="M263" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="264" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7079,19 +7082,13 @@
         <v>206</v>
       </c>
       <c r="C264" t="s">
-        <v>15</v>
-      </c>
-      <c r="D264" t="s">
-        <v>308</v>
-      </c>
-      <c r="J264" t="s">
-        <v>438</v>
+        <v>52</v>
       </c>
       <c r="L264" t="s">
-        <v>226</v>
-      </c>
-      <c r="M264" s="1" t="s">
-        <v>245</v>
+        <v>206</v>
+      </c>
+      <c r="M264" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="265" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7099,16 +7096,22 @@
         <v>77</v>
       </c>
       <c r="B265" t="s">
-        <v>148</v>
+        <v>206</v>
       </c>
       <c r="C265" t="s">
-        <v>9</v>
+        <v>15</v>
+      </c>
+      <c r="D265" t="s">
+        <v>308</v>
+      </c>
+      <c r="J265" t="s">
+        <v>438</v>
       </c>
       <c r="L265" t="s">
-        <v>148</v>
-      </c>
-      <c r="M265" t="s">
-        <v>125</v>
+        <v>226</v>
+      </c>
+      <c r="M265" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="266" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7116,16 +7119,16 @@
         <v>77</v>
       </c>
       <c r="B266" t="s">
-        <v>190</v>
+        <v>148</v>
       </c>
       <c r="C266" t="s">
-        <v>81</v>
+        <v>9</v>
       </c>
       <c r="L266" t="s">
-        <v>190</v>
+        <v>148</v>
       </c>
       <c r="M266" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="267" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7133,16 +7136,16 @@
         <v>77</v>
       </c>
       <c r="B267" t="s">
-        <v>380</v>
+        <v>190</v>
       </c>
       <c r="C267" t="s">
-        <v>9</v>
+        <v>81</v>
       </c>
       <c r="L267" t="s">
-        <v>380</v>
+        <v>190</v>
       </c>
       <c r="M267" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="268" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7150,19 +7153,16 @@
         <v>77</v>
       </c>
       <c r="B268" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C268" t="s">
-        <v>15</v>
-      </c>
-      <c r="H268" t="s">
-        <v>382</v>
+        <v>9</v>
       </c>
       <c r="L268" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="M268" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="269" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7170,16 +7170,19 @@
         <v>77</v>
       </c>
       <c r="B269" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C269" t="s">
-        <v>52</v>
+        <v>15</v>
+      </c>
+      <c r="H269" t="s">
+        <v>382</v>
       </c>
       <c r="L269" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="M269" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="270" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7190,36 +7193,36 @@
         <v>383</v>
       </c>
       <c r="C270" t="s">
-        <v>15</v>
-      </c>
-      <c r="D270" t="s">
-        <v>308</v>
-      </c>
-      <c r="J270" t="s">
-        <v>438</v>
+        <v>52</v>
       </c>
       <c r="L270" t="s">
-        <v>384</v>
-      </c>
-      <c r="M270" s="1" t="s">
-        <v>245</v>
+        <v>383</v>
+      </c>
+      <c r="M270" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="271" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="B271" t="s">
-        <v>115</v>
+        <v>383</v>
       </c>
       <c r="C271" t="s">
-        <v>9</v>
+        <v>15</v>
+      </c>
+      <c r="D271" t="s">
+        <v>308</v>
+      </c>
+      <c r="J271" t="s">
+        <v>438</v>
       </c>
       <c r="L271" t="s">
-        <v>115</v>
-      </c>
-      <c r="M271" t="s">
-        <v>120</v>
+        <v>384</v>
+      </c>
+      <c r="M271" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="272" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7227,28 +7230,16 @@
         <v>114</v>
       </c>
       <c r="B272" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C272" t="s">
         <v>9</v>
       </c>
-      <c r="D272" t="s">
-        <v>305</v>
-      </c>
-      <c r="F272" t="s">
-        <v>11</v>
-      </c>
-      <c r="H272" t="s">
-        <v>448</v>
-      </c>
-      <c r="I272" t="s">
-        <v>447</v>
-      </c>
       <c r="L272" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M272" t="s">
-        <v>149</v>
+        <v>120</v>
       </c>
     </row>
     <row r="273" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7256,16 +7247,28 @@
         <v>114</v>
       </c>
       <c r="B273" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C273" t="s">
-        <v>15</v>
+        <v>9</v>
+      </c>
+      <c r="D273" t="s">
+        <v>305</v>
+      </c>
+      <c r="F273" t="s">
+        <v>11</v>
+      </c>
+      <c r="H273" t="s">
+        <v>448</v>
+      </c>
+      <c r="I273" t="s">
+        <v>447</v>
       </c>
       <c r="L273" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M273" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
     </row>
     <row r="274" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7273,16 +7276,16 @@
         <v>114</v>
       </c>
       <c r="B274" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C274" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L274" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M274" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="275" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7290,13 +7293,13 @@
         <v>114</v>
       </c>
       <c r="B275" t="s">
-        <v>446</v>
+        <v>118</v>
       </c>
       <c r="C275" t="s">
         <v>17</v>
       </c>
       <c r="L275" t="s">
-        <v>446</v>
+        <v>118</v>
       </c>
       <c r="M275" t="s">
         <v>121</v>
@@ -7307,19 +7310,16 @@
         <v>114</v>
       </c>
       <c r="B276" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C276" t="s">
-        <v>9</v>
-      </c>
-      <c r="K276" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="L276" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="M276" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="277" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7327,16 +7327,19 @@
         <v>114</v>
       </c>
       <c r="B277" t="s">
-        <v>406</v>
+        <v>440</v>
       </c>
       <c r="C277" t="s">
-        <v>17</v>
+        <v>9</v>
+      </c>
+      <c r="K277" t="s">
+        <v>114</v>
       </c>
       <c r="L277" t="s">
-        <v>406</v>
+        <v>440</v>
       </c>
       <c r="M277" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="278" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7344,13 +7347,13 @@
         <v>114</v>
       </c>
       <c r="B278" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C278" t="s">
         <v>17</v>
       </c>
       <c r="L278" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="M278" t="s">
         <v>121</v>
@@ -7361,13 +7364,13 @@
         <v>114</v>
       </c>
       <c r="B279" t="s">
-        <v>268</v>
+        <v>411</v>
       </c>
       <c r="C279" t="s">
         <v>17</v>
       </c>
       <c r="L279" t="s">
-        <v>268</v>
+        <v>411</v>
       </c>
       <c r="M279" t="s">
         <v>121</v>
@@ -7378,25 +7381,13 @@
         <v>114</v>
       </c>
       <c r="B280" t="s">
-        <v>196</v>
+        <v>268</v>
       </c>
       <c r="C280" t="s">
-        <v>15</v>
-      </c>
-      <c r="D280" t="s">
-        <v>329</v>
-      </c>
-      <c r="E280" t="s">
-        <v>199</v>
-      </c>
-      <c r="F280" t="s">
-        <v>195</v>
-      </c>
-      <c r="G280" t="s">
-        <v>200</v>
+        <v>17</v>
       </c>
       <c r="L280" t="s">
-        <v>196</v>
+        <v>268</v>
       </c>
       <c r="M280" t="s">
         <v>121</v>
@@ -7407,13 +7398,25 @@
         <v>114</v>
       </c>
       <c r="B281" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C281" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+      <c r="D281" t="s">
+        <v>329</v>
+      </c>
+      <c r="E281" t="s">
+        <v>199</v>
+      </c>
+      <c r="F281" t="s">
+        <v>195</v>
+      </c>
+      <c r="G281" t="s">
+        <v>200</v>
       </c>
       <c r="L281" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M281" t="s">
         <v>121</v>
@@ -7424,16 +7427,16 @@
         <v>114</v>
       </c>
       <c r="B282" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C282" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="L282" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="M282" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="283" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7444,19 +7447,13 @@
         <v>198</v>
       </c>
       <c r="C283" t="s">
-        <v>15</v>
-      </c>
-      <c r="D283" t="s">
-        <v>308</v>
-      </c>
-      <c r="J283" t="s">
-        <v>438</v>
+        <v>52</v>
       </c>
       <c r="L283" t="s">
-        <v>225</v>
-      </c>
-      <c r="M283" s="1" t="s">
-        <v>245</v>
+        <v>198</v>
+      </c>
+      <c r="M283" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="284" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7464,19 +7461,22 @@
         <v>114</v>
       </c>
       <c r="B284" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C284" t="s">
-        <v>9</v>
-      </c>
-      <c r="K284" t="s">
-        <v>20</v>
+        <v>15</v>
+      </c>
+      <c r="D284" t="s">
+        <v>308</v>
+      </c>
+      <c r="J284" t="s">
+        <v>438</v>
       </c>
       <c r="L284" t="s">
-        <v>207</v>
-      </c>
-      <c r="M284" t="s">
-        <v>121</v>
+        <v>225</v>
+      </c>
+      <c r="M284" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="285" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7484,19 +7484,16 @@
         <v>114</v>
       </c>
       <c r="B285" t="s">
-        <v>407</v>
+        <v>207</v>
       </c>
       <c r="C285" t="s">
         <v>9</v>
       </c>
-      <c r="D285" t="s">
-        <v>310</v>
-      </c>
-      <c r="J285" t="s">
-        <v>416</v>
+      <c r="K285" t="s">
+        <v>20</v>
       </c>
       <c r="L285" t="s">
-        <v>407</v>
+        <v>207</v>
       </c>
       <c r="M285" t="s">
         <v>121</v>
@@ -7507,19 +7504,19 @@
         <v>114</v>
       </c>
       <c r="B286" t="s">
-        <v>216</v>
+        <v>407</v>
       </c>
       <c r="C286" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D286" t="s">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="J286" t="s">
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="L286" t="s">
-        <v>216</v>
+        <v>407</v>
       </c>
       <c r="M286" t="s">
         <v>121</v>
@@ -7527,19 +7524,25 @@
     </row>
     <row r="287" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>385</v>
+        <v>114</v>
       </c>
       <c r="B287" t="s">
-        <v>386</v>
+        <v>216</v>
       </c>
       <c r="C287" t="s">
-        <v>9</v>
+        <v>15</v>
+      </c>
+      <c r="D287" t="s">
+        <v>330</v>
+      </c>
+      <c r="J287" t="s">
+        <v>432</v>
       </c>
       <c r="L287" t="s">
-        <v>386</v>
+        <v>216</v>
       </c>
       <c r="M287" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="288" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7547,28 +7550,16 @@
         <v>385</v>
       </c>
       <c r="B288" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="C288" t="s">
         <v>9</v>
       </c>
-      <c r="D288" t="s">
-        <v>305</v>
-      </c>
-      <c r="F288" t="s">
-        <v>11</v>
-      </c>
-      <c r="H288" t="s">
-        <v>448</v>
-      </c>
-      <c r="I288" t="s">
-        <v>447</v>
-      </c>
       <c r="L288" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="M288" t="s">
-        <v>149</v>
+        <v>120</v>
       </c>
     </row>
     <row r="289" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7576,16 +7567,28 @@
         <v>385</v>
       </c>
       <c r="B289" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
       <c r="C289" t="s">
-        <v>15</v>
+        <v>9</v>
+      </c>
+      <c r="D289" t="s">
+        <v>305</v>
+      </c>
+      <c r="F289" t="s">
+        <v>11</v>
+      </c>
+      <c r="H289" t="s">
+        <v>448</v>
+      </c>
+      <c r="I289" t="s">
+        <v>447</v>
       </c>
       <c r="L289" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
       <c r="M289" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
     </row>
     <row r="290" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7593,16 +7596,16 @@
         <v>385</v>
       </c>
       <c r="B290" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C290" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="L290" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="M290" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="291" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7613,19 +7616,13 @@
         <v>388</v>
       </c>
       <c r="C291" t="s">
-        <v>15</v>
-      </c>
-      <c r="D291" t="s">
-        <v>308</v>
-      </c>
-      <c r="J291" t="s">
-        <v>438</v>
+        <v>52</v>
       </c>
       <c r="L291" t="s">
-        <v>389</v>
-      </c>
-      <c r="M291" s="1" t="s">
-        <v>245</v>
+        <v>388</v>
+      </c>
+      <c r="M291" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="292" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7633,22 +7630,22 @@
         <v>385</v>
       </c>
       <c r="B292" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C292" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D292" t="s">
-        <v>435</v>
+        <v>308</v>
       </c>
       <c r="J292" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="L292" t="s">
-        <v>390</v>
-      </c>
-      <c r="M292" t="s">
-        <v>121</v>
+        <v>389</v>
+      </c>
+      <c r="M292" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="293" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7656,19 +7653,19 @@
         <v>385</v>
       </c>
       <c r="B293" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C293" t="s">
         <v>9</v>
       </c>
       <c r="D293" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J293" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="L293" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="M293" t="s">
         <v>121</v>
@@ -7679,16 +7676,19 @@
         <v>385</v>
       </c>
       <c r="B294" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C294" t="s">
         <v>9</v>
       </c>
-      <c r="K294" t="s">
-        <v>39</v>
+      <c r="D294" t="s">
+        <v>436</v>
+      </c>
+      <c r="J294" t="s">
+        <v>434</v>
       </c>
       <c r="L294" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="M294" t="s">
         <v>121</v>
@@ -7699,16 +7699,16 @@
         <v>385</v>
       </c>
       <c r="B295" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C295" t="s">
         <v>9</v>
       </c>
-      <c r="J295" t="s">
-        <v>431</v>
+      <c r="K295" t="s">
+        <v>39</v>
       </c>
       <c r="L295" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="M295" t="s">
         <v>121</v>
@@ -7719,25 +7719,16 @@
         <v>385</v>
       </c>
       <c r="B296" t="s">
-        <v>450</v>
+        <v>393</v>
       </c>
       <c r="C296" t="s">
         <v>9</v>
       </c>
-      <c r="D296" t="s">
-        <v>451</v>
-      </c>
-      <c r="F296" t="s">
-        <v>11</v>
-      </c>
-      <c r="H296" t="s">
-        <v>452</v>
-      </c>
-      <c r="I296" t="s">
-        <v>453</v>
+      <c r="J296" t="s">
+        <v>431</v>
       </c>
       <c r="L296" t="s">
-        <v>450</v>
+        <v>393</v>
       </c>
       <c r="M296" t="s">
         <v>121</v>
@@ -7748,16 +7739,28 @@
         <v>385</v>
       </c>
       <c r="B297" t="s">
-        <v>394</v>
+        <v>450</v>
       </c>
       <c r="C297" t="s">
-        <v>15</v>
+        <v>9</v>
+      </c>
+      <c r="D297" t="s">
+        <v>451</v>
+      </c>
+      <c r="F297" t="s">
+        <v>11</v>
+      </c>
+      <c r="H297" t="s">
+        <v>452</v>
+      </c>
+      <c r="I297" t="s">
+        <v>453</v>
       </c>
       <c r="L297" t="s">
-        <v>394</v>
+        <v>450</v>
       </c>
       <c r="M297" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="298" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7765,13 +7768,13 @@
         <v>385</v>
       </c>
       <c r="B298" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C298" t="s">
         <v>15</v>
       </c>
       <c r="L298" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="M298" t="s">
         <v>122</v>
@@ -7782,19 +7785,16 @@
         <v>385</v>
       </c>
       <c r="B299" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C299" t="s">
         <v>15</v>
       </c>
-      <c r="J299" t="s">
-        <v>437</v>
-      </c>
       <c r="L299" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="M299" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="300" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7802,16 +7802,19 @@
         <v>385</v>
       </c>
       <c r="B300" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C300" t="s">
         <v>15</v>
       </c>
+      <c r="J300" t="s">
+        <v>437</v>
+      </c>
       <c r="L300" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="M300" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="301" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7819,16 +7822,16 @@
         <v>385</v>
       </c>
       <c r="B301" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C301" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L301" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="M301" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="302" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7836,13 +7839,13 @@
         <v>385</v>
       </c>
       <c r="B302" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C302" t="s">
         <v>17</v>
       </c>
       <c r="L302" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="M302" t="s">
         <v>121</v>
@@ -7853,13 +7856,13 @@
         <v>385</v>
       </c>
       <c r="B303" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C303" t="s">
         <v>17</v>
       </c>
       <c r="L303" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="M303" t="s">
         <v>121</v>
@@ -7870,16 +7873,16 @@
         <v>385</v>
       </c>
       <c r="B304" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C304" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L304" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="M304" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="305" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7887,18 +7890,35 @@
         <v>385</v>
       </c>
       <c r="B305" t="s">
+        <v>401</v>
+      </c>
+      <c r="C305" t="s">
+        <v>9</v>
+      </c>
+      <c r="L305" t="s">
+        <v>401</v>
+      </c>
+      <c r="M305" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="306" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>385</v>
+      </c>
+      <c r="B306" t="s">
         <v>402</v>
       </c>
-      <c r="C305" t="s">
-        <v>9</v>
-      </c>
-      <c r="K305" t="s">
-        <v>77</v>
-      </c>
-      <c r="L305" t="s">
+      <c r="C306" t="s">
+        <v>9</v>
+      </c>
+      <c r="K306" t="s">
+        <v>77</v>
+      </c>
+      <c r="L306" t="s">
         <v>402</v>
       </c>
-      <c r="M305" t="s">
+      <c r="M306" t="s">
         <v>121</v>
       </c>
     </row>

--- a/criterion_property_definitions.xlsx
+++ b/criterion_property_definitions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\configuration\master-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BEF0077-2C24-42D9-BD93-6940AED9DFEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EA08C86-2099-4477-8DAF-87FA7BC27135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="48570" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16470" yWindow="2160" windowWidth="48570" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="criterion_property" sheetId="4" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1839" uniqueCount="460">
   <si>
     <t>property</t>
   </si>
@@ -1405,6 +1405,9 @@
   </si>
   <si>
     <t>staff.personParticulars.cvAcademicTitle</t>
+  </si>
+  <si>
+    <t>completeTitle</t>
   </si>
 </sst>
 </file>
@@ -2373,6 +2376,9 @@
       <c r="C28" t="s">
         <v>15</v>
       </c>
+      <c r="H28" t="s">
+        <v>459</v>
+      </c>
       <c r="L28" t="s">
         <v>458</v>
       </c>

--- a/criterion_property_definitions.xlsx
+++ b/criterion_property_definitions.xlsx
@@ -1372,7 +1372,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>EQ, NE, GT, GE, LT, LE, LIKE, ILIKE</t>
+          <t>EQ, NE, GT, GE, LT, LE</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>EQ, NE, GT, GE, LT, LE, LIKE, ILIKE</t>
+          <t>EQ, NE, GT, GE, LT, LE</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>EQ, NE, GT, GE, LT, LE, LIKE, ILIKE</t>
+          <t>EQ, NE, GT, GE, LT, LE</t>
         </is>
       </c>
     </row>
@@ -4767,7 +4767,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>EQ, NE, LIKE, ILIKE</t>
+          <t>EQ, NE</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>EQ, NE, LIKE, ILIKE</t>
+          <t>EQ, NE</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>IS_NULL, EQ, NE, GT, GE, LT, LE, LIKE, ILIKE</t>
+          <t>IS_NULL, EQ, NE, GT, GE, LT, LE</t>
         </is>
       </c>
     </row>
